--- a/Egy_Nutri_Sales_Analysis_Template.xlsx
+++ b/Egy_Nutri_Sales_Analysis_Template.xlsx
@@ -7,28 +7,31 @@
     <sheet sheetId="1" name="Executive Summary" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Data_YTD_2026" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Data_2025" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Slide1_Contribution" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Slide2_Core_Averages" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Slide3_Specialty_Averages" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Slide4_Dual_Axis_DeepDive" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Slide5_Total_PPG_Ranking" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Slide6_Pediamil1_Ranking" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Slide7_Pediamil2_Ranking" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Slide8_PediaStart1_Ranking" state="visible" r:id="rId14"/>
-    <sheet sheetId="12" name="Slide9_PediaStart2_Ranking" state="visible" r:id="rId15"/>
-    <sheet sheetId="13" name="Slide10_Quadrant_Matrix" state="visible" r:id="rId16"/>
+    <sheet sheetId="4" name="Data_Avg_Q3_2026" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Data_Avg_H1_2026" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Slide1_Contribution" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Slide2_Core_Averages" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Slide3_Specialty_Averages" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Slide4_Dual_Axis_DeepDive" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Slide5_Total_PPG_Ranking" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Slide6_Pediamil1_Ranking" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Slide7_Pediamil2_Ranking" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Slide8_PediaStart1_Ranking" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="Slide9_PediaStart2_Ranking" state="visible" r:id="rId17"/>
+    <sheet sheetId="15" name="Slide10_Quadrant_Matrix" state="visible" r:id="rId18"/>
+    <sheet sheetId="16" name="11-Q3 vs H1 Rep Velocity" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="199">
-  <si>
-    <t>EGY NUTRI. - BUSINESS REVIEW &amp; SALES ANALYSIS TEMPLATE</t>
-  </si>
-  <si>
-    <t>Comparison: YTD June 2026 (6 Months Monthly Avg) vs Full Year 2025 (12 Months Monthly Avg)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="257">
+  <si>
+    <t>EGY NUTRI. - BUSINESS REVIEW &amp; SALES ANALYSIS MODEL</t>
+  </si>
+  <si>
+    <t>Updated Review: YTD September 2026 (9 Months Monthly Avg) vs Full Year 2025 (12 Months Monthly Avg) + Q3 vs H1 Rep Velocity</t>
   </si>
   <si>
     <t>Company YTD 2026 Units</t>
@@ -40,10 +43,10 @@
     <t>Company 2025 Total Units</t>
   </si>
   <si>
-    <t>6 Months (Jan-Jun 2026)</t>
-  </si>
-  <si>
-    <t>829,882 / 6 Months</t>
+    <t>9 Months (Jan-Sep 2026)</t>
+  </si>
+  <si>
+    <t>1,298,415 / 9 Months</t>
   </si>
   <si>
     <t>12 Months (Full Year)</t>
@@ -61,7 +64,7 @@
     <t>1,240,615 / 12 Months</t>
   </si>
   <si>
-    <t>Benchmark Growth Rate</t>
+    <t>Benchmark Growth Rate (+39.5%)</t>
   </si>
   <si>
     <t>National Coverage</t>
@@ -124,7 +127,7 @@
     <t>Total PPG% Growth Ranking</t>
   </si>
   <si>
-    <t>All 9 ADMs ranked by Total PPG%. Company at top (+33.79%), Green above, Red below.</t>
+    <t>All 9 ADMs ranked by Total PPG%. Company at top (+39.5%), Green above, Red below.</t>
   </si>
   <si>
     <t>Slide 6</t>
@@ -133,7 +136,7 @@
     <t>Pediamil 1 PPG% Ranking</t>
   </si>
   <si>
-    <t>Ranked by Pediamil 1 growth. Company (+39.92%) at top, Green above, Red below.</t>
+    <t>Ranked by Pediamil 1 growth. Company (+46.9%) at top, Green above, Red below.</t>
   </si>
   <si>
     <t>Slide 7</t>
@@ -142,7 +145,7 @@
     <t>Pediamil 2 PPG% Ranking</t>
   </si>
   <si>
-    <t>Ranked by Pediamil 2 growth. Company (+65.26%) at top, Green above, Red below.</t>
+    <t>Ranked by Pediamil 2 growth. Company (+68.5%) at top, Green above, Red below.</t>
   </si>
   <si>
     <t>Slide 8</t>
@@ -151,7 +154,7 @@
     <t>Pedia-Start 1 PPG% Ranking</t>
   </si>
   <si>
-    <t>Ranked by Pedia-Start 1 growth. Company (-2.06%) at top, Green above, Red below.</t>
+    <t>Ranked by Pedia-Start 1 growth. Company (+9.6%) at top, Green above, Red below.</t>
   </si>
   <si>
     <t>Slide 9</t>
@@ -160,7 +163,7 @@
     <t>Pedia-Start 2 PPG% Ranking</t>
   </si>
   <si>
-    <t>Ranked by Pedia-Start 2 growth. Company (+39.86%) at top, Green above, Red below.</t>
+    <t>Ranked by Pedia-Start 2 growth. Company (+37.6%) at top, Green above, Red below.</t>
   </si>
   <si>
     <t>Slide 10</t>
@@ -169,7 +172,16 @@
     <t>Strategic Quadrant Matrix</t>
   </si>
   <si>
-    <t>Bubble matrix: X=Contribution Diff (0 baseline), Y=PPG% (+33.79% baseline). Quadrants A/B/C/D.</t>
+    <t>Bubble matrix: X=Contribution Diff (0 baseline), Y=PPG% (+39.5% baseline). Quadrants A/B/C/D.</t>
+  </si>
+  <si>
+    <t>Slide 11</t>
+  </si>
+  <si>
+    <t>Rep Performance Velocity (Q3 vs H1)</t>
+  </si>
+  <si>
+    <t>Quarterly Run-Rate Comparison: Average Monthly Sales Q3 2026 vs H1 2026 baseline. 4 Velocity Tiers.</t>
   </si>
   <si>
     <t>Territory Name</t>
@@ -211,7 +223,7 @@
     <t>LBW- Egy</t>
   </si>
   <si>
-    <t>Sum YTD 6/2026</t>
+    <t>Sum YTD 9/2026</t>
   </si>
   <si>
     <t>Contribution % 2026</t>
@@ -427,7 +439,7 @@
     <t>Company Total PPG%:</t>
   </si>
   <si>
-    <t>STATUS: 🟢 ABOVE COMPANY BENCHMARK (+16.33% ahead of Egypt Growth)</t>
+    <t>STATUS: 🟢 ABOVE COMPANY BENCHMARK (+18.2% ahead of Egypt Growth)</t>
   </si>
   <si>
     <t>Product Name</t>
@@ -502,19 +514,13 @@
     <t>GREEN</t>
   </si>
   <si>
-    <t>Ahmed Hassan Abd-Elmonem</t>
-  </si>
-  <si>
     <t>🔻 BELOW COMPANY PPG</t>
   </si>
   <si>
     <t>RED</t>
   </si>
   <si>
-    <t>NOHER ADEL ABD EL- HAKEEM</t>
-  </si>
-  <si>
-    <t>SLIDE 6: PEDIAMIL 1 PPG% GROWTH RANKING (COMPANY AT TOP: +39.92%)</t>
+    <t>SLIDE 6: PEDIAMIL 1 PPG% GROWTH RANKING (COMPANY AT TOP: +46.9%)</t>
   </si>
   <si>
     <t>Pediamil 1 PPG%</t>
@@ -523,46 +529,52 @@
     <t>Bar Color</t>
   </si>
   <si>
-    <t>🟢 ABOVE COMPANY (39.9%)</t>
-  </si>
-  <si>
-    <t>🔻 BELOW COMPANY (39.9%)</t>
-  </si>
-  <si>
-    <t>SLIDE 7: PEDIAMIL 2 PPG% GROWTH RANKING (COMPANY AT TOP: +65.26%)</t>
+    <t>🟢 ABOVE COMPANY (46.9%)</t>
+  </si>
+  <si>
+    <t>🔻 BELOW COMPANY (46.9%)</t>
+  </si>
+  <si>
+    <t>SLIDE 7: PEDIAMIL 2 PPG% GROWTH RANKING (COMPANY AT TOP: +68.5%)</t>
   </si>
   <si>
     <t>Pediamil 2 PPG%</t>
   </si>
   <si>
-    <t>🟢 ABOVE COMPANY (65.3%)</t>
-  </si>
-  <si>
-    <t>🔻 BELOW COMPANY (65.3%)</t>
-  </si>
-  <si>
-    <t>SLIDE 8: PEDIA-START 1 PPG% GROWTH RANKING (COMPANY AT TOP: -2.06%)</t>
+    <t>🟢 ABOVE COMPANY (68.5%)</t>
+  </si>
+  <si>
+    <t>🔻 BELOW COMPANY (68.5%)</t>
+  </si>
+  <si>
+    <t>SLIDE 8: PEDIA-START 1 PPG% GROWTH RANKING (COMPANY AT TOP: +9.6%)</t>
   </si>
   <si>
     <t>Pedia-Start 1 PPG%</t>
   </si>
   <si>
-    <t>🟢 ABOVE COMPANY (-2.1%)</t>
-  </si>
-  <si>
-    <t>🔻 BELOW COMPANY (-2.1%)</t>
-  </si>
-  <si>
-    <t>SLIDE 9: PEDIA-START 2 PPG% GROWTH RANKING (COMPANY AT TOP: +39.86%)</t>
+    <t>🟢 ABOVE COMPANY (9.6%)</t>
+  </si>
+  <si>
+    <t>🔻 BELOW COMPANY (9.6%)</t>
+  </si>
+  <si>
+    <t>SLIDE 9: PEDIA-START 2 PPG% GROWTH RANKING (COMPANY AT TOP: +37.6%)</t>
   </si>
   <si>
     <t>Pedia-Start 2 PPG%</t>
   </si>
   <si>
+    <t>🟢 ABOVE COMPANY (37.6%)</t>
+  </si>
+  <si>
+    <t>🔻 BELOW COMPANY (37.6%)</t>
+  </si>
+  <si>
     <t>SLIDE 10: STRATEGIC QUADRANT MATRIX (CONTRIBUTION DIFF vs PPG%)</t>
   </si>
   <si>
-    <t>Baselines: X-Axis Reference = 0.00% (Contribution Diff) | Y-Axis Reference = +33.79% (Company Total PPG)</t>
+    <t>Baselines: X-Axis Reference = 0.00% (Contribution Diff) | Y-Axis Reference = +39.55% (Company Total PPG)</t>
   </si>
   <si>
     <t>Quadrant</t>
@@ -583,57 +595,223 @@
     <t>Strategic Classification &amp; Recommendation</t>
   </si>
   <si>
+    <t>Quadrant B</t>
+  </si>
+  <si>
+    <t>CHALLENGER: High growth outstripping company pace, rapidly closing territorial potential gap.</t>
+  </si>
+  <si>
+    <t>Quadrant C</t>
+  </si>
+  <si>
+    <t>VOLUME PILLAR: High market contribution defender; growth moderate, focus on specialty formulas.</t>
+  </si>
+  <si>
+    <t>Quadrant D</t>
+  </si>
+  <si>
+    <t>CRITICAL ATTENTION: Lowest performer; lagging growth and contribution gap below geographic share.</t>
+  </si>
+  <si>
     <t>Quadrant A</t>
   </si>
   <si>
-    <t>COMPANY STAR: Heavy volume, stellar growth (+60.2%), expanding market share.</t>
-  </si>
-  <si>
-    <t>COMPANY STAR: Giant territory, outstanding growth (+50.1%), strong execution.</t>
-  </si>
-  <si>
-    <t>Quadrant B</t>
-  </si>
-  <si>
-    <t>FAST GROWER / CHALLENGER: High growth (+39.6%) exceeding company, closing GEO gap.</t>
-  </si>
-  <si>
-    <t>Quadrant C</t>
-  </si>
-  <si>
-    <t>PILLAR / CORE BACKBONE: Massive contribution gain (+7.25%), solid growth (+32.2%).</t>
-  </si>
-  <si>
-    <t>SHARE GAINER: Contribution far outstripping GEO potential (7.6% vs 1.8% geo).</t>
-  </si>
-  <si>
-    <t>SHARE DEFENDER: Positive contribution diff, but growth (+14.9%) lagging company pace.</t>
-  </si>
-  <si>
-    <t>Quadrant D</t>
-  </si>
-  <si>
-    <t>LOWEST PERFORMER / ATTENTION: High potential territory (14.5%) losing share (-5.2%).</t>
-  </si>
-  <si>
-    <t>LOWEST PERFORMER / ATTENTION: Slower growth (+27.8%) and negative contribution diff.</t>
-  </si>
-  <si>
-    <t>CRITICAL PRIORITY: Massive capital market losing share (-8.29% diff), urgent turnaround.</t>
+    <t>COMPANY STAR: Heavy volume, high growth exceeding company benchmark, expanding market share.</t>
+  </si>
+  <si>
+    <t>SLIDE 11: MEDICAL REP / ADM QUARTERLY VELOCITY (AVERAGE MONTHLY Q3 2026 vs H1 2026 BASELINE)</t>
+  </si>
+  <si>
+    <t>National Velocity Benchmark: H1 Monthly Avg = 138,315 cans/mo | Q3 Monthly Avg = 156,126 cans/mo | Acceleration = +12.9% (+17,811 cans/mo)</t>
+  </si>
+  <si>
+    <t>Medical Rep / ADM Name</t>
+  </si>
+  <si>
+    <t>H1 MoAvg (Jan-Jun)</t>
+  </si>
+  <si>
+    <t>Q3 MoAvg (Jul-Sep)</t>
+  </si>
+  <si>
+    <t>Net Diff / Mo</t>
+  </si>
+  <si>
+    <t>Velocity %</t>
+  </si>
+  <si>
+    <t>Performance Tier</t>
+  </si>
+  <si>
+    <t>Strategic Velocity Assessment</t>
+  </si>
+  <si>
+    <t>National Medical Rep Team Benchmark</t>
+  </si>
+  <si>
+    <t>Overall company run-rate accelerated by +12.9% in Q3</t>
+  </si>
+  <si>
+    <t>Tier 1: High Accelerator 🚀</t>
+  </si>
+  <si>
+    <t>Exceptional momentum; staged dramatic turnaround driven by core and specialty clinic expansion.</t>
+  </si>
+  <si>
+    <t>Tier 2: Scale Compounder 📈</t>
+  </si>
+  <si>
+    <t>High-volume scale compounder; continues building market leadership at heavy volume.</t>
+  </si>
+  <si>
+    <t>Tier 3: Steady Consolidator 🛡️</t>
+  </si>
+  <si>
+    <t>Stable baseline preserved; requires activation of secondary core &amp; specialty products to reignite growth.</t>
+  </si>
+  <si>
+    <t>Tier 4: Contraction Watchlist ⚠️</t>
+  </si>
+  <si>
+    <t>Quarterly run-rate deceleration; urgent trade stock replenishment and rep detailing call review.</t>
+  </si>
+  <si>
+    <t>PRODUCT PORTFOLIO VELOCITY BREAKDOWN (Q3 2026 vs H1 2026)</t>
+  </si>
+  <si>
+    <t>SKU Code</t>
+  </si>
+  <si>
+    <t>Product Description</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>H1 MoAvg (Units)</t>
+  </si>
+  <si>
+    <t>Q3 MoAvg (Units)</t>
+  </si>
+  <si>
+    <t>Diff / Mo</t>
+  </si>
+  <si>
+    <t>Supply / Demand Dynamic</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>Core Infant</t>
+  </si>
+  <si>
+    <t>Strong demand (+10.5%), supply stable</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>Core Follow-up</t>
+  </si>
+  <si>
+    <t>Slight dip (-8.4%) from peak Q2 promotions</t>
+  </si>
+  <si>
+    <t>PG3</t>
+  </si>
+  <si>
+    <t>Growing Up Milk</t>
+  </si>
+  <si>
+    <t>Supply constraint in Q3 (-80.6%)</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Specialty Lactose Free</t>
+  </si>
+  <si>
+    <t>Supply quota restricted (-46.2%)</t>
+  </si>
+  <si>
+    <t>HA</t>
+  </si>
+  <si>
+    <t>Specialty Hypoallergenic</t>
+  </si>
+  <si>
+    <t>Surge in hospital demand (+102.4%)</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>Specialty Anti-Regurgitation</t>
+  </si>
+  <si>
+    <t>Steady pediatric adoption (+30.1%)</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>Specialty Anti-Colic</t>
+  </si>
+  <si>
+    <t>Massive surge across clinics (+101.9%)</t>
+  </si>
+  <si>
+    <t>MUM</t>
+  </si>
+  <si>
+    <t>Maternal Nutrition</t>
+  </si>
+  <si>
+    <t>Niche pharmacy detailing (-10.4%)</t>
+  </si>
+  <si>
+    <t>PS1</t>
+  </si>
+  <si>
+    <t>Economy Infant</t>
+  </si>
+  <si>
+    <t>Heavy clinic uptake across Upper Egypt (+35.7%)</t>
+  </si>
+  <si>
+    <t>PS2</t>
+  </si>
+  <si>
+    <t>Economy Follow-up</t>
+  </si>
+  <si>
+    <t>Stable rural demand (-6.3%)</t>
+  </si>
+  <si>
+    <t>LBW</t>
+  </si>
+  <si>
+    <t>Specialty Low Birth Weight</t>
+  </si>
+  <si>
+    <t>Severe temporary stockout in Q3 (-98.8%)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="+0.0%;-0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="+0.00%;-0.00%"/>
     <numFmt numFmtId="167" formatCode="+0.00%"/>
     <numFmt numFmtId="168" formatCode="+#,##0;-#,##0"/>
+    <numFmt numFmtId="169" formatCode="+0.0%"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -717,22 +895,19 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF155724"/>
-    </font>
-    <font>
-      <b/>
       <color rgb="FF0C5460"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF856404"/>
+      <color rgb="856404"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF721C24"/>
+      <i/>
+      <color rgb="FF4A5568"/>
+      <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -771,22 +946,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD1ECF1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
+        <fgColor rgb="FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -802,7 +967,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -867,8 +1032,21 @@
     <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="17" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="18" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1208,13 +1386,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:G25"/>
+  <dimension ref="A2:G26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" ht="35" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
@@ -1253,11 +1431,11 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="4">
-        <v>829882</v>
+        <v>1298415</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>138314</v>
+        <v>144268</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4">
@@ -1299,7 +1477,7 @@
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="6">
-        <v>0.33785</v>
+        <v>0.3954530615863907</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="7">
@@ -1483,8 +1661,22 @@
       <c r="F25"/>
       <c r="G25"/>
     </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+    </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="32">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B5:C5"/>
@@ -1516,6 +1708,7 @@
     <mergeCell ref="D23:G23"/>
     <mergeCell ref="D24:G24"/>
     <mergeCell ref="D25:G25"/>
+    <mergeCell ref="D26:G26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1538,7 +1731,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -1550,54 +1743,54 @@
     </row>
     <row r="2" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="37" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D3" s="38">
-        <v>14774.5</v>
+        <v>103384.58333333333</v>
       </c>
       <c r="E3" s="38">
-        <v>24416.666666666668</v>
+        <v>144268.33333333334</v>
       </c>
       <c r="F3" s="39">
-        <v>0.6526</v>
+        <v>0.3954530615863907</v>
       </c>
       <c r="G3" s="37" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H3" s="37" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1605,25 +1798,25 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D4" s="12">
-        <v>1967</v>
+        <v>14859.333333333334</v>
       </c>
       <c r="E4" s="12">
-        <v>4794</v>
+        <v>23434.555555555555</v>
       </c>
       <c r="F4" s="40">
-        <v>1.4372</v>
+        <v>0.577093334529738</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="H4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1631,25 +1824,25 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D5" s="12">
-        <v>2045</v>
+        <v>7151.5</v>
       </c>
       <c r="E5" s="12">
-        <v>3843</v>
+        <v>10471.222222222223</v>
       </c>
       <c r="F5" s="40">
-        <v>0.8789</v>
+        <v>0.4641994298010519</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="H5" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1657,25 +1850,25 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>159</v>
+        <v>83</v>
       </c>
       <c r="D6" s="12">
-        <v>815</v>
+        <v>12877</v>
       </c>
       <c r="E6" s="12">
-        <v>1478</v>
+        <v>18827.333333333332</v>
       </c>
       <c r="F6" s="40">
-        <v>0.8139</v>
+        <v>0.4620900313219951</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="H6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -1683,22 +1876,22 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D7" s="12">
-        <v>2640</v>
+        <v>14223.833333333334</v>
       </c>
       <c r="E7" s="12">
-        <v>4201</v>
-      </c>
-      <c r="F7" s="41">
-        <v>0.5912</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>171</v>
+        <v>20761.777777777777</v>
+      </c>
+      <c r="F7" s="40">
+        <v>0.45964714934636297</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>160</v>
       </c>
       <c r="H7" t="s">
         <v>161</v>
@@ -1709,22 +1902,22 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" t="s">
         <v>71</v>
       </c>
-      <c r="C8" t="s">
-        <v>162</v>
-      </c>
       <c r="D8" s="12">
-        <v>1204</v>
+        <v>7308.666666666667</v>
       </c>
       <c r="E8" s="12">
-        <v>1837</v>
-      </c>
-      <c r="F8" s="41">
-        <v>0.5267</v>
-      </c>
-      <c r="G8" s="25" t="s">
-        <v>171</v>
+        <v>10242</v>
+      </c>
+      <c r="F8" s="40">
+        <v>0.4013499954392046</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>160</v>
       </c>
       <c r="H8" t="s">
         <v>161</v>
@@ -1735,25 +1928,25 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D9" s="12">
-        <v>1920</v>
+        <v>9950.916666666666</v>
       </c>
       <c r="E9" s="12">
-        <v>2808</v>
+        <v>13216.555555555555</v>
       </c>
       <c r="F9" s="41">
-        <v>0.4625</v>
+        <v>0.32817467960796476</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1761,25 +1954,25 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="D10" s="12">
-        <v>1365</v>
+        <v>9336.5</v>
       </c>
       <c r="E10" s="12">
-        <v>1841</v>
+        <v>12131.111111111111</v>
       </c>
       <c r="F10" s="41">
-        <v>0.3484</v>
+        <v>0.2993210636867254</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -1787,25 +1980,25 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D11" s="12">
-        <v>1217</v>
+        <v>15235.416666666666</v>
       </c>
       <c r="E11" s="12">
-        <v>1575</v>
+        <v>19635.333333333332</v>
       </c>
       <c r="F11" s="41">
-        <v>0.2942</v>
+        <v>0.2887952960481335</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1813,25 +2006,25 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" t="s">
         <v>73</v>
       </c>
-      <c r="C12" t="s">
-        <v>74</v>
-      </c>
       <c r="D12" s="12">
-        <v>1602</v>
+        <v>12441.416666666666</v>
       </c>
       <c r="E12" s="12">
-        <v>2041</v>
+        <v>15548.444444444445</v>
       </c>
       <c r="F12" s="41">
-        <v>0.2736</v>
+        <v>0.24973263584220273</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -1859,7 +2052,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -1871,54 +2064,54 @@
     </row>
     <row r="2" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="37" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D3" s="38">
-        <v>24790.5</v>
+        <v>27891.083333333332</v>
       </c>
       <c r="E3" s="38">
-        <v>24279</v>
+        <v>40960.333333333336</v>
       </c>
       <c r="F3" s="39">
-        <v>-0.0206</v>
+        <v>0.4685816554275113</v>
       </c>
       <c r="G3" s="37" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H3" s="37" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1926,25 +2119,25 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D4" s="12">
-        <v>3422</v>
+        <v>1712.1666666666667</v>
       </c>
       <c r="E4" s="12">
-        <v>4025</v>
+        <v>3277.6666666666665</v>
       </c>
       <c r="F4" s="40">
-        <v>0.1762</v>
+        <v>0.9143385573834322</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="H4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1952,25 +2145,25 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="D5" s="12">
-        <v>1609</v>
+        <v>4877</v>
       </c>
       <c r="E5" s="12">
-        <v>1888</v>
+        <v>7890</v>
       </c>
       <c r="F5" s="40">
-        <v>0.1736</v>
+        <v>0.6177978265327044</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="H5" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1978,25 +2171,25 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D6" s="12">
-        <v>3701</v>
+        <v>1968.75</v>
       </c>
       <c r="E6" s="12">
-        <v>3931</v>
+        <v>3084.777777777778</v>
       </c>
       <c r="F6" s="40">
-        <v>0.0623</v>
+        <v>0.5668712522045856</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="H6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -2004,25 +2197,25 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D7" s="12">
-        <v>2581</v>
+        <v>3800.4166666666665</v>
       </c>
       <c r="E7" s="12">
-        <v>2567</v>
-      </c>
-      <c r="F7" s="40">
-        <v>-0.0055</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>174</v>
+        <v>5549.666666666667</v>
+      </c>
+      <c r="F7" s="41">
+        <v>0.4602784782370355</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="H7" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -2030,25 +2223,25 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D8" s="12">
-        <v>3588</v>
+        <v>1816.3333333333333</v>
       </c>
       <c r="E8" s="12">
-        <v>3392</v>
+        <v>2607.5555555555557</v>
       </c>
       <c r="F8" s="41">
-        <v>-0.0547</v>
+        <v>0.4356150975714199</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="H8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -2056,25 +2249,25 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="D9" s="12">
-        <v>950</v>
+        <v>2608.3333333333335</v>
       </c>
       <c r="E9" s="12">
-        <v>862</v>
+        <v>3632.222222222222</v>
       </c>
       <c r="F9" s="41">
-        <v>-0.0933</v>
+        <v>0.39254526091586794</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="H9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -2082,25 +2275,25 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
         <v>83</v>
       </c>
-      <c r="C10" t="s">
-        <v>84</v>
-      </c>
       <c r="D10" s="12">
-        <v>2864</v>
+        <v>3766.5833333333335</v>
       </c>
       <c r="E10" s="12">
-        <v>2555</v>
+        <v>5217.777777777777</v>
       </c>
       <c r="F10" s="41">
-        <v>-0.1081</v>
+        <v>0.3852813852813852</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="H10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -2108,25 +2301,25 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="D11" s="12">
-        <v>2496</v>
+        <v>4024</v>
       </c>
       <c r="E11" s="12">
-        <v>2159</v>
+        <v>5458.444444444444</v>
       </c>
       <c r="F11" s="41">
-        <v>-0.135</v>
+        <v>0.3564722774464324</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="H11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -2134,25 +2327,25 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D12" s="12">
-        <v>3579</v>
+        <v>3317.5</v>
       </c>
       <c r="E12" s="12">
-        <v>2901</v>
+        <v>4242.222222222223</v>
       </c>
       <c r="F12" s="41">
-        <v>-0.1896</v>
+        <v>0.2787406849200369</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="H12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -2180,7 +2373,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -2192,54 +2385,54 @@
     </row>
     <row r="2" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="37" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D3" s="38">
-        <v>11607.166666666666</v>
+        <v>14774.5</v>
       </c>
       <c r="E3" s="38">
-        <v>16234.333333333334</v>
+        <v>24900.333333333332</v>
       </c>
       <c r="F3" s="39">
-        <v>0.3986</v>
+        <v>0.685358782587115</v>
       </c>
       <c r="G3" s="37" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H3" s="37" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2247,25 +2440,25 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D4" s="12">
-        <v>1822</v>
+        <v>1966.8333333333333</v>
       </c>
       <c r="E4" s="12">
-        <v>3685</v>
+        <v>4469.444444444444</v>
       </c>
       <c r="F4" s="40">
-        <v>1.0227</v>
+        <v>1.2724062932519842</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -2273,25 +2466,25 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D5" s="12">
-        <v>722</v>
+        <v>814.9166666666666</v>
       </c>
       <c r="E5" s="12">
-        <v>1286</v>
+        <v>1518</v>
       </c>
       <c r="F5" s="40">
-        <v>0.7818</v>
+        <v>0.8627671541057369</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H5" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -2299,25 +2492,25 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D6" s="12">
-        <v>1528</v>
+        <v>1919.8333333333333</v>
       </c>
       <c r="E6" s="12">
-        <v>2428</v>
+        <v>3327</v>
       </c>
       <c r="F6" s="40">
-        <v>0.5895</v>
+        <v>0.7329629308099661</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -2325,25 +2518,25 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D7" s="12">
-        <v>1292</v>
+        <v>1203.5</v>
       </c>
       <c r="E7" s="12">
-        <v>1829</v>
+        <v>2069</v>
       </c>
       <c r="F7" s="40">
-        <v>0.4155</v>
+        <v>0.7191524719567928</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H7" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -2351,25 +2544,25 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D8" s="12">
-        <v>1404</v>
+        <v>2045.25</v>
       </c>
       <c r="E8" s="12">
-        <v>1926</v>
+        <v>3388.3333333333335</v>
       </c>
       <c r="F8" s="41">
-        <v>0.3714</v>
+        <v>0.6566841869372124</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="H8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -2377,25 +2570,25 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D9" s="12">
-        <v>1627</v>
+        <v>1365.3333333333333</v>
       </c>
       <c r="E9" s="12">
-        <v>1952</v>
+        <v>2126.3333333333335</v>
       </c>
       <c r="F9" s="41">
-        <v>0.1995</v>
+        <v>0.5573730468750002</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="H9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -2403,25 +2596,25 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="D10" s="12">
-        <v>947</v>
+        <v>1216.5833333333333</v>
       </c>
       <c r="E10" s="12">
-        <v>1094</v>
+        <v>1885.7777777777778</v>
       </c>
       <c r="F10" s="41">
-        <v>0.1553</v>
+        <v>0.5500605064273809</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="H10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -2429,25 +2622,25 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D11" s="12">
-        <v>1632</v>
+        <v>2640.0833333333335</v>
       </c>
       <c r="E11" s="12">
-        <v>1529</v>
+        <v>4054.4444444444443</v>
       </c>
       <c r="F11" s="41">
-        <v>-0.0632</v>
+        <v>0.5357259345769809</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="H11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -2455,25 +2648,25 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="D12" s="12">
-        <v>633</v>
+        <v>1602.1666666666667</v>
       </c>
       <c r="E12" s="12">
-        <v>505</v>
+        <v>2062</v>
       </c>
       <c r="F12" s="41">
-        <v>-0.2023</v>
+        <v>0.28700717778008933</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="H12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -2490,16 +2683,18 @@
   <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="38" customWidth="1"/>
+    <col min="4" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -2509,9 +2704,649 @@
       <c r="G1" s="23"/>
       <c r="H1" s="23"/>
     </row>
+    <row r="2" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="37" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="D3" s="38">
+        <v>24790.5</v>
+      </c>
+      <c r="E3" s="38">
+        <v>27169.555555555555</v>
+      </c>
+      <c r="F3" s="39">
+        <v>0.09596642082876716</v>
+      </c>
+      <c r="G3" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="H3" s="37" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="12">
+        <v>3422.0833333333335</v>
+      </c>
+      <c r="E4" s="12">
+        <v>4922.444444444444</v>
+      </c>
+      <c r="F4" s="40">
+        <v>0.43843500142051206</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="H4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="12">
+        <v>950.1666666666666</v>
+      </c>
+      <c r="E5" s="12">
+        <v>1259.111111111111</v>
+      </c>
+      <c r="F5" s="40">
+        <v>0.3251476349178506</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="H5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="12">
+        <v>1608.5</v>
+      </c>
+      <c r="E6" s="12">
+        <v>2118.222222222222</v>
+      </c>
+      <c r="F6" s="40">
+        <v>0.316892895382171</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="H6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="12">
+        <v>3588.4166666666665</v>
+      </c>
+      <c r="E7" s="12">
+        <v>3873.1111111111113</v>
+      </c>
+      <c r="F7" s="41">
+        <v>0.07933706447442779</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="H7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="12">
+        <v>2864.3333333333335</v>
+      </c>
+      <c r="E8" s="12">
+        <v>2956.1111111111113</v>
+      </c>
+      <c r="F8" s="41">
+        <v>0.03204158423523018</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="H8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="12">
+        <v>3579.0833333333335</v>
+      </c>
+      <c r="E9" s="12">
+        <v>3686.777777777778</v>
+      </c>
+      <c r="F9" s="41">
+        <v>0.030089951648078594</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="H9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="12">
+        <v>2581</v>
+      </c>
+      <c r="E10" s="12">
+        <v>2507.4444444444443</v>
+      </c>
+      <c r="F10" s="41">
+        <v>-0.028498859184639902</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="H10" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="12">
+        <v>3700.8333333333335</v>
+      </c>
+      <c r="E11" s="12">
+        <v>3548.1111111111113</v>
+      </c>
+      <c r="F11" s="41">
+        <v>-0.04126698191098099</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="H11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="12">
+        <v>2496.0833333333335</v>
+      </c>
+      <c r="E12" s="12">
+        <v>2298.222222222222</v>
+      </c>
+      <c r="F12" s="41">
+        <v>-0.07926863196786083</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="H12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+    </row>
+    <row r="2" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="37" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="D3" s="38">
+        <v>11607.166666666666</v>
+      </c>
+      <c r="E3" s="38">
+        <v>15969.222222222223</v>
+      </c>
+      <c r="F3" s="39">
+        <v>0.37580709236152</v>
+      </c>
+      <c r="G3" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="H3" s="37" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="12">
+        <v>1821.9166666666667</v>
+      </c>
+      <c r="E4" s="12">
+        <v>3049.4444444444443</v>
+      </c>
+      <c r="F4" s="40">
+        <v>0.6737562701062676</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="H4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="12">
+        <v>1527.75</v>
+      </c>
+      <c r="E5" s="12">
+        <v>2552.5555555555557</v>
+      </c>
+      <c r="F5" s="40">
+        <v>0.6707940144366262</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="H5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="12">
+        <v>721.9166666666666</v>
+      </c>
+      <c r="E6" s="12">
+        <v>1124.2222222222222</v>
+      </c>
+      <c r="F6" s="40">
+        <v>0.5572742314055947</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="H6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="12">
+        <v>1627.3333333333333</v>
+      </c>
+      <c r="E7" s="12">
+        <v>2182.1111111111113</v>
+      </c>
+      <c r="F7" s="41">
+        <v>0.3409121944558242</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="H7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="12">
+        <v>1292.3333333333333</v>
+      </c>
+      <c r="E8" s="12">
+        <v>1672.6666666666667</v>
+      </c>
+      <c r="F8" s="41">
+        <v>0.2942997162754708</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="H8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="12">
+        <v>1404</v>
+      </c>
+      <c r="E9" s="12">
+        <v>1799.3333333333333</v>
+      </c>
+      <c r="F9" s="41">
+        <v>0.2815764482431149</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="H9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="12">
+        <v>1632.1666666666667</v>
+      </c>
+      <c r="E10" s="12">
+        <v>1876.111111111111</v>
+      </c>
+      <c r="F10" s="41">
+        <v>0.14946049899588143</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="H10" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="12">
+        <v>946.6666666666666</v>
+      </c>
+      <c r="E11" s="12">
+        <v>1047.3333333333333</v>
+      </c>
+      <c r="F11" s="41">
+        <v>0.10633802816901405</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="H11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="12">
+        <v>633.0833333333334</v>
+      </c>
+      <c r="E12" s="12">
+        <v>665.4444444444445</v>
+      </c>
+      <c r="F12" s="41">
+        <v>0.051116668860515135</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="H12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="42" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+    </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="42" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
@@ -2523,268 +3358,1000 @@
     </row>
     <row r="3" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="43" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D4" s="12">
-        <v>136700</v>
+        <v>92178</v>
       </c>
       <c r="E4" s="12">
-        <v>22783</v>
+        <v>10242</v>
       </c>
       <c r="F4" s="16">
-        <v>0.042</v>
+        <v>-0.03</v>
       </c>
       <c r="G4" s="44">
-        <v>0.6018</v>
+        <v>0.4013499954392046</v>
       </c>
       <c r="H4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
-        <v>186</v>
+      <c r="A5" s="45" t="s">
+        <v>191</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D5" s="12">
-        <v>133831</v>
+        <v>139936</v>
       </c>
       <c r="E5" s="12">
-        <v>22305</v>
+        <v>15548.444444444445</v>
       </c>
       <c r="F5" s="16">
-        <v>0.0052</v>
+        <v>0.0102</v>
       </c>
       <c r="G5" s="44">
-        <v>0.5011</v>
+        <v>0.24973263584220273</v>
       </c>
       <c r="H5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="43" t="s">
         <v>189</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>159</v>
+        <v>75</v>
       </c>
       <c r="D6" s="12">
-        <v>61235</v>
+        <v>94241</v>
       </c>
       <c r="E6" s="12">
-        <v>10206</v>
+        <v>10471.222222222223</v>
       </c>
       <c r="F6" s="16">
-        <v>-0.0272</v>
+        <v>-0.0736</v>
       </c>
       <c r="G6" s="44">
-        <v>0.3964</v>
+        <v>0.4641994298010519</v>
       </c>
       <c r="H6" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="B7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="12">
+        <v>118949</v>
+      </c>
+      <c r="E7" s="12">
+        <v>13216.555555555555</v>
+      </c>
+      <c r="F7" s="16">
+        <v>-0.0536</v>
+      </c>
+      <c r="G7" s="44">
+        <v>0.32817467960796476</v>
+      </c>
+      <c r="H7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="45" t="s">
         <v>191</v>
       </c>
-      <c r="B7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" s="12">
-        <v>120877</v>
-      </c>
-      <c r="E7" s="12">
-        <v>20146</v>
-      </c>
-      <c r="F7" s="16">
-        <v>0.0725</v>
-      </c>
-      <c r="G7" s="44">
-        <v>0.3223</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="B8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="12">
+        <v>176718</v>
+      </c>
+      <c r="E8" s="12">
+        <v>19635.333333333332</v>
+      </c>
+      <c r="F8" s="16">
+        <v>0.0629</v>
+      </c>
+      <c r="G8" s="44">
+        <v>0.2887952960481335</v>
+      </c>
+      <c r="H8" t="s">
         <v>192</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="46" t="s">
-        <v>191</v>
-      </c>
-      <c r="B8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" s="12">
-        <v>62763</v>
-      </c>
-      <c r="E8" s="12">
-        <v>10461</v>
-      </c>
-      <c r="F8" s="16">
-        <v>0.058</v>
-      </c>
-      <c r="G8" s="44">
-        <v>0.1204</v>
-      </c>
-      <c r="H8" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="46" t="s">
+        <v>195</v>
+      </c>
+      <c r="B9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="12">
+        <v>186856</v>
+      </c>
+      <c r="E9" s="12">
+        <v>20761.777777777777</v>
+      </c>
+      <c r="F9" s="16">
+        <v>0.0212</v>
+      </c>
+      <c r="G9" s="44">
+        <v>0.45964714934636297</v>
+      </c>
+      <c r="H9" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="12">
+        <v>169446</v>
+      </c>
+      <c r="E10" s="12">
+        <v>18827.333333333332</v>
+      </c>
+      <c r="F10" s="16">
+        <v>-0.0099</v>
+      </c>
+      <c r="G10" s="44">
+        <v>0.4620900313219951</v>
+      </c>
+      <c r="H10" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="46" t="s">
+        <v>195</v>
+      </c>
+      <c r="B11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="12">
+        <v>210911</v>
+      </c>
+      <c r="E11" s="12">
+        <v>23434.555555555555</v>
+      </c>
+      <c r="F11" s="16">
+        <v>0.0063</v>
+      </c>
+      <c r="G11" s="44">
+        <v>0.577093334529738</v>
+      </c>
+      <c r="H11" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="45" t="s">
         <v>191</v>
       </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="12">
-        <v>85811</v>
-      </c>
-      <c r="E9" s="12">
-        <v>14302</v>
-      </c>
-      <c r="F9" s="16">
-        <v>0.0059</v>
-      </c>
-      <c r="G9" s="44">
-        <v>0.1495</v>
-      </c>
-      <c r="H9" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="47" t="s">
-        <v>195</v>
-      </c>
-      <c r="B10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" s="12">
-        <v>77368</v>
-      </c>
-      <c r="E10" s="12">
-        <v>12895</v>
-      </c>
-      <c r="F10" s="16">
-        <v>-0.052</v>
-      </c>
-      <c r="G10" s="44">
-        <v>0.2958</v>
-      </c>
-      <c r="H10" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="47" t="s">
-        <v>195</v>
-      </c>
-      <c r="B11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" s="12">
-        <v>98752</v>
-      </c>
-      <c r="E11" s="12">
-        <v>16459</v>
-      </c>
-      <c r="F11" s="16">
-        <v>-0.0214</v>
-      </c>
-      <c r="G11" s="44">
-        <v>0.2781</v>
-      </c>
-      <c r="H11" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="47" t="s">
-        <v>195</v>
-      </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>162</v>
+        <v>87</v>
       </c>
       <c r="D12" s="12">
-        <v>52545</v>
+        <v>109180</v>
       </c>
       <c r="E12" s="12">
-        <v>8758</v>
+        <v>12131.111111111111</v>
       </c>
       <c r="F12" s="16">
-        <v>-0.0829</v>
+        <v>0.0665</v>
       </c>
       <c r="G12" s="44">
-        <v>0.2246</v>
+        <v>0.2993210636867254</v>
       </c>
       <c r="H12" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="44" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="47" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+    </row>
+    <row r="3" ht="25" customHeight="1" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="37" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="38">
+        <v>138315</v>
+      </c>
+      <c r="E4" s="38">
+        <v>156126</v>
+      </c>
+      <c r="F4" s="48">
+        <v>17811</v>
+      </c>
+      <c r="G4" s="49">
+        <v>0.12877128294111273</v>
+      </c>
+      <c r="H4" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="I4" s="37" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="12">
+        <v>8758</v>
+      </c>
+      <c r="E5" s="12">
+        <v>13898</v>
+      </c>
+      <c r="F5" s="32">
+        <v>5140</v>
+      </c>
+      <c r="G5" s="50">
+        <v>0.5868919844713405</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="I5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="12">
+        <v>10461</v>
+      </c>
+      <c r="E6" s="12">
+        <v>15472</v>
+      </c>
+      <c r="F6" s="32">
+        <v>5011</v>
+      </c>
+      <c r="G6" s="50">
+        <v>0.47901730236115103</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="I6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="12">
+        <v>16459</v>
+      </c>
+      <c r="E7" s="12">
+        <v>23564</v>
+      </c>
+      <c r="F7" s="32">
+        <v>7105</v>
+      </c>
+      <c r="G7" s="50">
+        <v>0.43167871681147085</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="I7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="12">
+        <v>14302</v>
+      </c>
+      <c r="E8" s="12">
+        <v>18041</v>
+      </c>
+      <c r="F8" s="32">
+        <v>3739</v>
+      </c>
+      <c r="G8" s="51">
+        <v>0.26143196755698495</v>
+      </c>
+      <c r="H8" s="52" t="s">
+        <v>210</v>
+      </c>
+      <c r="I8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="12">
+        <v>22305</v>
+      </c>
+      <c r="E9" s="12">
+        <v>25694</v>
+      </c>
+      <c r="F9" s="32">
+        <v>3389</v>
+      </c>
+      <c r="G9" s="51">
+        <v>0.15193902712396334</v>
+      </c>
+      <c r="H9" s="52" t="s">
+        <v>210</v>
+      </c>
+      <c r="I9" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="12">
+        <v>12895</v>
+      </c>
+      <c r="E10" s="12">
+        <v>13858</v>
+      </c>
+      <c r="F10" s="32">
+        <v>963</v>
+      </c>
+      <c r="G10" s="53">
+        <v>0.07468010856921281</v>
+      </c>
+      <c r="H10" s="54" t="s">
+        <v>212</v>
+      </c>
+      <c r="I10" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="12">
+        <v>10206</v>
+      </c>
+      <c r="E11" s="12">
+        <v>10314</v>
+      </c>
+      <c r="F11" s="32">
+        <v>108</v>
+      </c>
+      <c r="G11" s="53">
+        <v>0.010582010582010692</v>
+      </c>
+      <c r="H11" s="54" t="s">
+        <v>212</v>
+      </c>
+      <c r="I11" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="12">
+        <v>20146</v>
+      </c>
+      <c r="E12" s="12">
+        <v>18614</v>
+      </c>
+      <c r="F12" s="32">
+        <v>-1532</v>
+      </c>
+      <c r="G12" s="55">
+        <v>-0.07604487243125191</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="I12" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="12">
+        <v>22783</v>
+      </c>
+      <c r="E13" s="12">
+        <v>16671</v>
+      </c>
+      <c r="F13" s="32">
+        <v>-6112</v>
+      </c>
+      <c r="G13" s="55">
+        <v>-0.26827020146600533</v>
+      </c>
+      <c r="H13" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="I13" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+    </row>
+    <row r="16" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>224</v>
+      </c>
+      <c r="B17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" t="s">
+        <v>225</v>
+      </c>
+      <c r="D17" s="12">
+        <v>39024</v>
+      </c>
+      <c r="E17" s="12">
+        <v>44832</v>
+      </c>
+      <c r="F17" s="32">
+        <v>5808</v>
+      </c>
+      <c r="G17" s="56">
+        <v>0.14883148831488313</v>
+      </c>
+      <c r="H17" t="s">
+        <v>226</v>
+      </c>
+      <c r="I17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>227</v>
+      </c>
+      <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
+        <v>228</v>
+      </c>
+      <c r="D18" s="12">
+        <v>24418</v>
+      </c>
+      <c r="E18" s="12">
+        <v>25866</v>
+      </c>
+      <c r="F18" s="32">
+        <v>1448</v>
+      </c>
+      <c r="G18" s="56">
+        <v>0.05930051601277753</v>
+      </c>
+      <c r="H18" t="s">
+        <v>229</v>
+      </c>
+      <c r="I18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" t="s">
+        <v>231</v>
+      </c>
+      <c r="D19" s="12">
+        <v>5338</v>
+      </c>
+      <c r="E19" s="12">
+        <v>1038</v>
+      </c>
+      <c r="F19" s="32">
+        <v>-4300</v>
+      </c>
+      <c r="G19" s="57">
+        <v>-0.8055451479955039</v>
+      </c>
+      <c r="H19" t="s">
+        <v>232</v>
+      </c>
+      <c r="I19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>233</v>
+      </c>
+      <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" t="s">
+        <v>234</v>
+      </c>
+      <c r="D20" s="12">
+        <v>4335</v>
+      </c>
+      <c r="E20" s="12">
+        <v>2331</v>
+      </c>
+      <c r="F20" s="32">
+        <v>-2004</v>
+      </c>
+      <c r="G20" s="57">
+        <v>-0.46228373702422143</v>
+      </c>
+      <c r="H20" t="s">
+        <v>235</v>
+      </c>
+      <c r="I20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>236</v>
+      </c>
+      <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
+        <v>237</v>
+      </c>
+      <c r="D21" s="12">
+        <v>5899</v>
+      </c>
+      <c r="E21" s="12">
+        <v>11939</v>
+      </c>
+      <c r="F21" s="32">
+        <v>6040</v>
+      </c>
+      <c r="G21" s="58">
+        <v>1.0239023563315817</v>
+      </c>
+      <c r="H21" t="s">
+        <v>238</v>
+      </c>
+      <c r="I21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>239</v>
+      </c>
+      <c r="B22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" t="s">
+        <v>240</v>
+      </c>
+      <c r="D22" s="12">
+        <v>4676</v>
+      </c>
+      <c r="E22" s="12">
+        <v>5970</v>
+      </c>
+      <c r="F22" s="32">
+        <v>1294</v>
+      </c>
+      <c r="G22" s="58">
+        <v>0.27673224978614197</v>
+      </c>
+      <c r="H22" t="s">
+        <v>241</v>
+      </c>
+      <c r="I22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>242</v>
+      </c>
+      <c r="B23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" t="s">
+        <v>243</v>
+      </c>
+      <c r="D23" s="12">
+        <v>7519</v>
+      </c>
+      <c r="E23" s="12">
+        <v>15180</v>
+      </c>
+      <c r="F23" s="32">
+        <v>7661</v>
+      </c>
+      <c r="G23" s="58">
+        <v>1.0188854900917677</v>
+      </c>
+      <c r="H23" t="s">
+        <v>244</v>
+      </c>
+      <c r="I23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>245</v>
+      </c>
+      <c r="B24" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" t="s">
+        <v>246</v>
+      </c>
+      <c r="D24" s="12">
+        <v>722</v>
+      </c>
+      <c r="E24" s="12">
+        <v>583</v>
+      </c>
+      <c r="F24" s="32">
+        <v>-139</v>
+      </c>
+      <c r="G24" s="57">
+        <v>-0.19252077562326875</v>
+      </c>
+      <c r="H24" t="s">
+        <v>247</v>
+      </c>
+      <c r="I24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>248</v>
+      </c>
+      <c r="B25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" t="s">
+        <v>249</v>
+      </c>
+      <c r="D25" s="12">
+        <v>24280</v>
+      </c>
+      <c r="E25" s="12">
+        <v>32950</v>
+      </c>
+      <c r="F25" s="32">
+        <v>8670</v>
+      </c>
+      <c r="G25" s="58">
+        <v>0.35708401976935744</v>
+      </c>
+      <c r="H25" t="s">
+        <v>250</v>
+      </c>
+      <c r="I25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>251</v>
+      </c>
+      <c r="B26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" t="s">
+        <v>252</v>
+      </c>
+      <c r="D26" s="12">
+        <v>16234</v>
+      </c>
+      <c r="E26" s="12">
+        <v>15438</v>
+      </c>
+      <c r="F26" s="32">
+        <v>-796</v>
+      </c>
+      <c r="G26" s="57">
+        <v>-0.04903289392632748</v>
+      </c>
+      <c r="H26" t="s">
+        <v>253</v>
+      </c>
+      <c r="I26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>254</v>
+      </c>
+      <c r="B27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" t="s">
+        <v>255</v>
+      </c>
+      <c r="D27" s="12">
+        <v>5871</v>
+      </c>
+      <c r="E27" s="12">
+        <v>49</v>
+      </c>
+      <c r="F27" s="32">
+        <v>-5822</v>
+      </c>
+      <c r="G27" s="57">
+        <v>-0.9916538920115824</v>
+      </c>
+      <c r="H27" t="s">
+        <v>256</v>
+      </c>
+      <c r="I27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B15:I15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2802,606 +4369,606 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O1" s="11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C2" s="12">
-        <v>19436</v>
+        <v>29499</v>
       </c>
       <c r="D2" s="12">
-        <v>8869</v>
+        <v>13662</v>
       </c>
       <c r="E2" s="12">
-        <v>2538</v>
+        <v>2715</v>
       </c>
       <c r="F2" s="12">
-        <v>1527</v>
+        <v>2005</v>
       </c>
       <c r="G2" s="12">
-        <v>2260</v>
+        <v>4399</v>
       </c>
       <c r="H2" s="12">
-        <v>1895</v>
+        <v>3000</v>
       </c>
       <c r="I2" s="12">
-        <v>2136</v>
+        <v>3681</v>
       </c>
       <c r="J2" s="12">
-        <v>350</v>
+        <v>395</v>
       </c>
       <c r="K2" s="12">
-        <v>12955</v>
+        <v>20684</v>
       </c>
       <c r="L2" s="12">
-        <v>6562</v>
+        <v>9426</v>
       </c>
       <c r="M2" s="12">
-        <v>2707</v>
+        <v>2712</v>
       </c>
       <c r="N2" s="12">
-        <v>61235</v>
+        <v>92178</v>
       </c>
       <c r="O2" s="13">
-        <v>0.073787598718854</v>
+        <v>0.07099271034299512</v>
       </c>
       <c r="P2" s="14">
-        <v>0.10101</v>
+        <v>0.101</v>
       </c>
       <c r="Q2" s="15">
-        <v>0.730478862</v>
+        <v>0.702810642</v>
       </c>
       <c r="R2" s="16">
-        <v>-0.0272</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C3" s="12">
-        <v>23500</v>
+        <v>38180</v>
       </c>
       <c r="D3" s="12">
-        <v>11046</v>
+        <v>19137</v>
       </c>
       <c r="E3" s="12">
-        <v>2651</v>
+        <v>2965</v>
       </c>
       <c r="F3" s="12">
-        <v>2578</v>
+        <v>3206</v>
       </c>
       <c r="G3" s="12">
-        <v>4457</v>
+        <v>8740</v>
       </c>
       <c r="H3" s="12">
-        <v>3572</v>
+        <v>5593</v>
       </c>
       <c r="I3" s="12">
-        <v>4660</v>
+        <v>8843</v>
       </c>
       <c r="J3" s="12">
-        <v>387</v>
+        <v>456</v>
       </c>
       <c r="K3" s="12">
-        <v>17403</v>
+        <v>33181</v>
       </c>
       <c r="L3" s="12">
-        <v>10976</v>
+        <v>15054</v>
       </c>
       <c r="M3" s="12">
         <v>4581</v>
       </c>
       <c r="N3" s="12">
-        <v>85811</v>
+        <v>139936</v>
       </c>
       <c r="O3" s="13">
-        <v>0.10340144743469554</v>
+        <v>0.10777447888386994</v>
       </c>
       <c r="P3" s="14">
-        <v>0.09754</v>
+        <v>0.0975</v>
       </c>
       <c r="Q3" s="15">
-        <v>1.06014107</v>
+        <v>1.104977553</v>
       </c>
       <c r="R3" s="16">
-        <v>0.0059</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C4" s="12">
-        <v>15452</v>
+        <v>27763</v>
       </c>
       <c r="D4" s="12">
-        <v>11024</v>
+        <v>18621</v>
       </c>
       <c r="E4" s="12">
-        <v>3206</v>
+        <v>3521</v>
       </c>
       <c r="F4" s="12">
-        <v>2574</v>
+        <v>3813</v>
       </c>
       <c r="G4" s="12">
-        <v>2990</v>
+        <v>6153</v>
       </c>
       <c r="H4" s="12">
-        <v>2240</v>
+        <v>3773</v>
       </c>
       <c r="I4" s="12">
-        <v>3813</v>
+        <v>10022</v>
       </c>
       <c r="J4" s="12">
-        <v>561</v>
+        <v>731</v>
       </c>
       <c r="K4" s="12">
-        <v>5169</v>
+        <v>11332</v>
       </c>
       <c r="L4" s="12">
-        <v>3030</v>
+        <v>5989</v>
       </c>
       <c r="M4" s="12">
-        <v>2486</v>
+        <v>2523</v>
       </c>
       <c r="N4" s="12">
-        <v>52545</v>
+        <v>94241</v>
       </c>
       <c r="O4" s="13">
-        <v>0.0633162305002398</v>
+        <v>0.07258157060724037</v>
       </c>
       <c r="P4" s="14">
-        <v>0.14619</v>
+        <v>0.1462</v>
       </c>
       <c r="Q4" s="15">
-        <v>0.433104767</v>
+        <v>0.496482779</v>
       </c>
       <c r="R4" s="16">
-        <v>-0.0829</v>
+        <v>-0.0736</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C5" s="12">
-        <v>20510</v>
+        <v>32690</v>
       </c>
       <c r="D5" s="12">
-        <v>12243</v>
+        <v>18558</v>
       </c>
       <c r="E5" s="12">
-        <v>2582</v>
+        <v>2828</v>
       </c>
       <c r="F5" s="12">
-        <v>4260</v>
+        <v>5047</v>
       </c>
       <c r="G5" s="12">
-        <v>4196</v>
+        <v>8593</v>
       </c>
       <c r="H5" s="12">
-        <v>3300</v>
+        <v>5391</v>
       </c>
       <c r="I5" s="12">
-        <v>6343</v>
+        <v>11160</v>
       </c>
       <c r="J5" s="12">
-        <v>1381</v>
+        <v>1943</v>
       </c>
       <c r="K5" s="12">
-        <v>11326</v>
+        <v>19064</v>
       </c>
       <c r="L5" s="12">
-        <v>7718</v>
+        <v>10118</v>
       </c>
       <c r="M5" s="12">
-        <v>3509</v>
+        <v>3557</v>
       </c>
       <c r="N5" s="12">
-        <v>77368</v>
+        <v>118949</v>
       </c>
       <c r="O5" s="13">
-        <v>0.09322771189157013</v>
+        <v>0.09161092562855482</v>
       </c>
       <c r="P5" s="14">
-        <v>0.14525</v>
+        <v>0.1453</v>
       </c>
       <c r="Q5" s="15">
-        <v>0.641847568</v>
+        <v>0.630716309</v>
       </c>
       <c r="R5" s="16">
-        <v>-0.052</v>
+        <v>-0.0536</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C6" s="12">
-        <v>32885</v>
+        <v>49126</v>
       </c>
       <c r="D6" s="12">
-        <v>25206</v>
+        <v>36490</v>
       </c>
       <c r="E6" s="12">
-        <v>6882</v>
+        <v>7610</v>
       </c>
       <c r="F6" s="12">
-        <v>3744</v>
+        <v>4465</v>
       </c>
       <c r="G6" s="12">
-        <v>6222</v>
+        <v>11724</v>
       </c>
       <c r="H6" s="12">
-        <v>5424</v>
+        <v>8538</v>
       </c>
       <c r="I6" s="12">
-        <v>7790</v>
+        <v>14062</v>
       </c>
       <c r="J6" s="12">
-        <v>421</v>
+        <v>593</v>
       </c>
       <c r="K6" s="12">
-        <v>15401</v>
+        <v>22567</v>
       </c>
       <c r="L6" s="12">
-        <v>11553</v>
+        <v>16194</v>
       </c>
       <c r="M6" s="12">
         <v>5349</v>
       </c>
       <c r="N6" s="12">
-        <v>120877</v>
+        <v>176718</v>
       </c>
       <c r="O6" s="13">
-        <v>0.14565564742939358</v>
+        <v>0.13610286387634155</v>
       </c>
       <c r="P6" s="14">
-        <v>0.07317</v>
+        <v>0.0732</v>
       </c>
       <c r="Q6" s="15">
-        <v>1.990588131</v>
+        <v>1.86003562</v>
       </c>
       <c r="R6" s="16">
-        <v>0.0725</v>
+        <v>0.0629</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C7" s="12">
-        <v>36545</v>
+        <v>49947</v>
       </c>
       <c r="D7" s="12">
-        <v>23057</v>
+        <v>30495</v>
       </c>
       <c r="E7" s="12">
-        <v>3777</v>
+        <v>4130</v>
       </c>
       <c r="F7" s="12">
-        <v>5016</v>
+        <v>5819</v>
       </c>
       <c r="G7" s="12">
-        <v>6509</v>
+        <v>11828</v>
       </c>
       <c r="H7" s="12">
-        <v>3126</v>
+        <v>4760</v>
       </c>
       <c r="I7" s="12">
-        <v>7430</v>
+        <v>14826</v>
       </c>
       <c r="J7" s="12">
-        <v>358</v>
+        <v>490</v>
       </c>
       <c r="K7" s="12">
-        <v>23588</v>
+        <v>31933</v>
       </c>
       <c r="L7" s="12">
-        <v>22111</v>
+        <v>27445</v>
       </c>
       <c r="M7" s="12">
         <v>5183</v>
       </c>
       <c r="N7" s="12">
-        <v>136700</v>
+        <v>186856</v>
       </c>
       <c r="O7" s="13">
-        <v>0.1647222135195124</v>
+        <v>0.1439108451458124</v>
       </c>
       <c r="P7" s="14">
-        <v>0.12271</v>
+        <v>0.1227</v>
       </c>
       <c r="Q7" s="15">
-        <v>1.342339456</v>
+        <v>1.172745094</v>
       </c>
       <c r="R7" s="16">
-        <v>0.042</v>
+        <v>0.0212</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C8" s="12">
-        <v>26168</v>
+        <v>46960</v>
       </c>
       <c r="D8" s="12">
-        <v>16847</v>
+        <v>29943</v>
       </c>
       <c r="E8" s="12">
-        <v>2530</v>
+        <v>2733</v>
       </c>
       <c r="F8" s="12">
-        <v>2031</v>
+        <v>2926</v>
       </c>
       <c r="G8" s="12">
-        <v>2240</v>
+        <v>4023</v>
       </c>
       <c r="H8" s="12">
-        <v>3269</v>
+        <v>4666</v>
       </c>
       <c r="I8" s="12">
-        <v>3832</v>
+        <v>7619</v>
       </c>
       <c r="J8" s="12">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="K8" s="12">
-        <v>24150</v>
+        <v>44302</v>
       </c>
       <c r="L8" s="12">
-        <v>14570</v>
+        <v>22973</v>
       </c>
       <c r="M8" s="12">
-        <v>2978</v>
+        <v>3016</v>
       </c>
       <c r="N8" s="12">
-        <v>98752</v>
+        <v>169446</v>
       </c>
       <c r="O8" s="13">
-        <v>0.11899523064724865</v>
+        <v>0.1305021892076108</v>
       </c>
       <c r="P8" s="14">
-        <v>0.14039</v>
+        <v>0.1404</v>
       </c>
       <c r="Q8" s="15">
-        <v>0.84761038</v>
+        <v>0.929574974</v>
       </c>
       <c r="R8" s="16">
-        <v>-0.0214</v>
+        <v>-0.0099</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C9" s="12">
-        <v>44494</v>
+        <v>71010</v>
       </c>
       <c r="D9" s="12">
-        <v>28761</v>
+        <v>40225</v>
       </c>
       <c r="E9" s="12">
-        <v>4173</v>
+        <v>4564</v>
       </c>
       <c r="F9" s="12">
-        <v>2908</v>
+        <v>3918</v>
       </c>
       <c r="G9" s="12">
-        <v>4618</v>
+        <v>9156</v>
       </c>
       <c r="H9" s="12">
-        <v>4106</v>
+        <v>7503</v>
       </c>
       <c r="I9" s="12">
-        <v>6659</v>
+        <v>13651</v>
       </c>
       <c r="J9" s="12">
-        <v>548</v>
+        <v>871</v>
       </c>
       <c r="K9" s="12">
-        <v>20353</v>
+        <v>34858</v>
       </c>
       <c r="L9" s="12">
-        <v>11712</v>
+        <v>19639</v>
       </c>
       <c r="M9" s="12">
-        <v>5499</v>
+        <v>5516</v>
       </c>
       <c r="N9" s="12">
-        <v>133831</v>
+        <v>210911</v>
       </c>
       <c r="O9" s="13">
-        <v>0.161265095519604</v>
+        <v>0.1624372792982213</v>
       </c>
       <c r="P9" s="14">
-        <v>0.15611</v>
+        <v>0.1561</v>
       </c>
       <c r="Q9" s="15">
-        <v>1.033014434</v>
+        <v>1.040522878</v>
       </c>
       <c r="R9" s="16">
-        <v>0.0052</v>
+        <v>0.0063</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C10" s="12">
-        <v>15157</v>
+        <v>23468</v>
       </c>
       <c r="D10" s="12">
-        <v>9447</v>
+        <v>16972</v>
       </c>
       <c r="E10" s="12">
-        <v>3685</v>
+        <v>4070</v>
       </c>
       <c r="F10" s="12">
-        <v>1370</v>
+        <v>1805</v>
       </c>
       <c r="G10" s="12">
-        <v>1902</v>
+        <v>6593</v>
       </c>
       <c r="H10" s="12">
-        <v>1129</v>
+        <v>2745</v>
       </c>
       <c r="I10" s="12">
-        <v>2450</v>
+        <v>6789</v>
       </c>
       <c r="J10" s="12">
-        <v>185</v>
+        <v>313</v>
       </c>
       <c r="K10" s="12">
-        <v>15329</v>
+        <v>26605</v>
       </c>
       <c r="L10" s="12">
-        <v>9174</v>
+        <v>16885</v>
       </c>
       <c r="M10" s="12">
         <v>2935</v>
       </c>
       <c r="N10" s="12">
-        <v>62763</v>
+        <v>109180</v>
       </c>
       <c r="O10" s="13">
-        <v>0.07562882433888192</v>
+        <v>0.08408713700935372</v>
       </c>
       <c r="P10" s="14">
-        <v>0.01763</v>
+        <v>0.0176</v>
       </c>
       <c r="Q10" s="15">
-        <v>4.290709151</v>
+        <v>4.770580276</v>
       </c>
       <c r="R10" s="16">
-        <v>0.058</v>
+        <v>0.0665</v>
       </c>
     </row>
     <row r="11" spans="1:18" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C11" s="18">
-        <v>234147</v>
+        <v>368643</v>
       </c>
       <c r="D11" s="18">
-        <v>146500</v>
+        <v>224103</v>
       </c>
       <c r="E11" s="18">
-        <v>32024</v>
+        <v>35136</v>
       </c>
       <c r="F11" s="18">
-        <v>26008</v>
+        <v>33004</v>
       </c>
       <c r="G11" s="18">
-        <v>35394</v>
+        <v>71209</v>
       </c>
       <c r="H11" s="18">
-        <v>28061</v>
+        <v>45969</v>
       </c>
       <c r="I11" s="18">
-        <v>45113</v>
+        <v>90653</v>
       </c>
       <c r="J11" s="18">
-        <v>4328</v>
+        <v>6077</v>
       </c>
       <c r="K11" s="18">
-        <v>145674</v>
+        <v>244526</v>
       </c>
       <c r="L11" s="18">
-        <v>97406</v>
+        <v>143723</v>
       </c>
       <c r="M11" s="18">
-        <v>35227</v>
+        <v>35372</v>
       </c>
       <c r="N11" s="18">
-        <v>829882</v>
+        <v>1298415</v>
       </c>
       <c r="O11" s="19">
         <v>1</v>
@@ -3433,57 +5000,57 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="O1" s="11" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C2" s="12">
         <v>20546</v>
@@ -3527,10 +5094,10 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C3" s="12">
         <v>39810</v>
@@ -3574,10 +5141,10 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C4" s="12">
         <v>23625</v>
@@ -3621,10 +5188,10 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C5" s="12">
         <v>31300</v>
@@ -3668,10 +5235,10 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C6" s="12">
         <v>48288</v>
@@ -3715,10 +5282,10 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C7" s="12">
         <v>45605</v>
@@ -3762,10 +5329,10 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C8" s="12">
         <v>45199</v>
@@ -3809,10 +5376,10 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C9" s="12">
         <v>58524</v>
@@ -3856,10 +5423,10 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C10" s="12">
         <v>21796</v>
@@ -3903,10 +5470,10 @@
     </row>
     <row r="11" spans="1:15" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C11" s="18">
         <v>334693</v>
@@ -3955,6 +5522,916 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="2" width="26" customWidth="1"/>
+    <col min="3" max="14" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2">
+        <v>3354</v>
+      </c>
+      <c r="D2">
+        <v>1598</v>
+      </c>
+      <c r="E2">
+        <v>59</v>
+      </c>
+      <c r="F2">
+        <v>159</v>
+      </c>
+      <c r="G2">
+        <v>713</v>
+      </c>
+      <c r="H2">
+        <v>368</v>
+      </c>
+      <c r="I2">
+        <v>515</v>
+      </c>
+      <c r="J2">
+        <v>15</v>
+      </c>
+      <c r="K2">
+        <v>2576</v>
+      </c>
+      <c r="L2">
+        <v>955</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+      <c r="N2">
+        <v>10314</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3">
+        <v>4893</v>
+      </c>
+      <c r="D3">
+        <v>2697</v>
+      </c>
+      <c r="E3">
+        <v>105</v>
+      </c>
+      <c r="F3">
+        <v>209</v>
+      </c>
+      <c r="G3">
+        <v>1428</v>
+      </c>
+      <c r="H3">
+        <v>674</v>
+      </c>
+      <c r="I3">
+        <v>1394</v>
+      </c>
+      <c r="J3">
+        <v>23</v>
+      </c>
+      <c r="K3">
+        <v>5259</v>
+      </c>
+      <c r="L3">
+        <v>1359</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>18041</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4">
+        <v>4104</v>
+      </c>
+      <c r="D4">
+        <v>2532</v>
+      </c>
+      <c r="E4">
+        <v>105</v>
+      </c>
+      <c r="F4">
+        <v>413</v>
+      </c>
+      <c r="G4">
+        <v>1054</v>
+      </c>
+      <c r="H4">
+        <v>511</v>
+      </c>
+      <c r="I4">
+        <v>2070</v>
+      </c>
+      <c r="J4">
+        <v>57</v>
+      </c>
+      <c r="K4">
+        <v>2054</v>
+      </c>
+      <c r="L4">
+        <v>986</v>
+      </c>
+      <c r="M4">
+        <v>12</v>
+      </c>
+      <c r="N4">
+        <v>13898</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5">
+        <v>4060</v>
+      </c>
+      <c r="D5">
+        <v>2105</v>
+      </c>
+      <c r="E5">
+        <v>82</v>
+      </c>
+      <c r="F5">
+        <v>262</v>
+      </c>
+      <c r="G5">
+        <v>1466</v>
+      </c>
+      <c r="H5">
+        <v>697</v>
+      </c>
+      <c r="I5">
+        <v>1606</v>
+      </c>
+      <c r="J5">
+        <v>187</v>
+      </c>
+      <c r="K5">
+        <v>2579</v>
+      </c>
+      <c r="L5">
+        <v>800</v>
+      </c>
+      <c r="M5">
+        <v>16</v>
+      </c>
+      <c r="N5">
+        <v>13858</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6">
+        <v>5414</v>
+      </c>
+      <c r="D6">
+        <v>3761</v>
+      </c>
+      <c r="E6">
+        <v>243</v>
+      </c>
+      <c r="F6">
+        <v>240</v>
+      </c>
+      <c r="G6">
+        <v>1834</v>
+      </c>
+      <c r="H6">
+        <v>1038</v>
+      </c>
+      <c r="I6">
+        <v>2091</v>
+      </c>
+      <c r="J6">
+        <v>57</v>
+      </c>
+      <c r="K6">
+        <v>2389</v>
+      </c>
+      <c r="L6">
+        <v>1547</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>18614</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7">
+        <v>4467</v>
+      </c>
+      <c r="D7">
+        <v>2479</v>
+      </c>
+      <c r="E7">
+        <v>118</v>
+      </c>
+      <c r="F7">
+        <v>268</v>
+      </c>
+      <c r="G7">
+        <v>1773</v>
+      </c>
+      <c r="H7">
+        <v>545</v>
+      </c>
+      <c r="I7">
+        <v>2465</v>
+      </c>
+      <c r="J7">
+        <v>44</v>
+      </c>
+      <c r="K7">
+        <v>2782</v>
+      </c>
+      <c r="L7">
+        <v>1778</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>16671</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8">
+        <v>6931</v>
+      </c>
+      <c r="D8">
+        <v>4365</v>
+      </c>
+      <c r="E8">
+        <v>68</v>
+      </c>
+      <c r="F8">
+        <v>298</v>
+      </c>
+      <c r="G8">
+        <v>594</v>
+      </c>
+      <c r="H8">
+        <v>466</v>
+      </c>
+      <c r="I8">
+        <v>1262</v>
+      </c>
+      <c r="J8">
+        <v>49</v>
+      </c>
+      <c r="K8">
+        <v>6717</v>
+      </c>
+      <c r="L8">
+        <v>2801</v>
+      </c>
+      <c r="M8">
+        <v>13</v>
+      </c>
+      <c r="N8">
+        <v>23564</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9">
+        <v>8839</v>
+      </c>
+      <c r="D9">
+        <v>3821</v>
+      </c>
+      <c r="E9">
+        <v>130</v>
+      </c>
+      <c r="F9">
+        <v>337</v>
+      </c>
+      <c r="G9">
+        <v>1513</v>
+      </c>
+      <c r="H9">
+        <v>1132</v>
+      </c>
+      <c r="I9">
+        <v>2331</v>
+      </c>
+      <c r="J9">
+        <v>108</v>
+      </c>
+      <c r="K9">
+        <v>4835</v>
+      </c>
+      <c r="L9">
+        <v>2642</v>
+      </c>
+      <c r="M9">
+        <v>6</v>
+      </c>
+      <c r="N9">
+        <v>25694</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10">
+        <v>2770</v>
+      </c>
+      <c r="D10">
+        <v>2508</v>
+      </c>
+      <c r="E10">
+        <v>128</v>
+      </c>
+      <c r="F10">
+        <v>145</v>
+      </c>
+      <c r="G10">
+        <v>1564</v>
+      </c>
+      <c r="H10">
+        <v>539</v>
+      </c>
+      <c r="I10">
+        <v>1446</v>
+      </c>
+      <c r="J10">
+        <v>43</v>
+      </c>
+      <c r="K10">
+        <v>3759</v>
+      </c>
+      <c r="L10">
+        <v>2570</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>15472</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="2" width="26" customWidth="1"/>
+    <col min="3" max="14" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2">
+        <v>3239</v>
+      </c>
+      <c r="D2">
+        <v>1478</v>
+      </c>
+      <c r="E2">
+        <v>423</v>
+      </c>
+      <c r="F2">
+        <v>254</v>
+      </c>
+      <c r="G2">
+        <v>377</v>
+      </c>
+      <c r="H2">
+        <v>316</v>
+      </c>
+      <c r="I2">
+        <v>356</v>
+      </c>
+      <c r="J2">
+        <v>58</v>
+      </c>
+      <c r="K2">
+        <v>2159</v>
+      </c>
+      <c r="L2">
+        <v>1094</v>
+      </c>
+      <c r="M2">
+        <v>451</v>
+      </c>
+      <c r="N2">
+        <v>10206</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3">
+        <v>3917</v>
+      </c>
+      <c r="D3">
+        <v>1841</v>
+      </c>
+      <c r="E3">
+        <v>442</v>
+      </c>
+      <c r="F3">
+        <v>430</v>
+      </c>
+      <c r="G3">
+        <v>743</v>
+      </c>
+      <c r="H3">
+        <v>595</v>
+      </c>
+      <c r="I3">
+        <v>777</v>
+      </c>
+      <c r="J3">
+        <v>65</v>
+      </c>
+      <c r="K3">
+        <v>2901</v>
+      </c>
+      <c r="L3">
+        <v>1829</v>
+      </c>
+      <c r="M3">
+        <v>763</v>
+      </c>
+      <c r="N3">
+        <v>14302</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4">
+        <v>2575</v>
+      </c>
+      <c r="D4">
+        <v>1837</v>
+      </c>
+      <c r="E4">
+        <v>534</v>
+      </c>
+      <c r="F4">
+        <v>429</v>
+      </c>
+      <c r="G4">
+        <v>498</v>
+      </c>
+      <c r="H4">
+        <v>373</v>
+      </c>
+      <c r="I4">
+        <v>636</v>
+      </c>
+      <c r="J4">
+        <v>94</v>
+      </c>
+      <c r="K4">
+        <v>862</v>
+      </c>
+      <c r="L4">
+        <v>505</v>
+      </c>
+      <c r="M4">
+        <v>414</v>
+      </c>
+      <c r="N4">
+        <v>8758</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5">
+        <v>3418</v>
+      </c>
+      <c r="D5">
+        <v>2041</v>
+      </c>
+      <c r="E5">
+        <v>430</v>
+      </c>
+      <c r="F5">
+        <v>710</v>
+      </c>
+      <c r="G5">
+        <v>699</v>
+      </c>
+      <c r="H5">
+        <v>550</v>
+      </c>
+      <c r="I5">
+        <v>1057</v>
+      </c>
+      <c r="J5">
+        <v>230</v>
+      </c>
+      <c r="K5">
+        <v>1888</v>
+      </c>
+      <c r="L5">
+        <v>1286</v>
+      </c>
+      <c r="M5">
+        <v>585</v>
+      </c>
+      <c r="N5">
+        <v>12895</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6">
+        <v>5481</v>
+      </c>
+      <c r="D6">
+        <v>4201</v>
+      </c>
+      <c r="E6">
+        <v>1147</v>
+      </c>
+      <c r="F6">
+        <v>624</v>
+      </c>
+      <c r="G6">
+        <v>1037</v>
+      </c>
+      <c r="H6">
+        <v>904</v>
+      </c>
+      <c r="I6">
+        <v>1298</v>
+      </c>
+      <c r="J6">
+        <v>70</v>
+      </c>
+      <c r="K6">
+        <v>2567</v>
+      </c>
+      <c r="L6">
+        <v>1926</v>
+      </c>
+      <c r="M6">
+        <v>892</v>
+      </c>
+      <c r="N6">
+        <v>20146</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7">
+        <v>6091</v>
+      </c>
+      <c r="D7">
+        <v>3843</v>
+      </c>
+      <c r="E7">
+        <v>630</v>
+      </c>
+      <c r="F7">
+        <v>836</v>
+      </c>
+      <c r="G7">
+        <v>1085</v>
+      </c>
+      <c r="H7">
+        <v>521</v>
+      </c>
+      <c r="I7">
+        <v>1238</v>
+      </c>
+      <c r="J7">
+        <v>60</v>
+      </c>
+      <c r="K7">
+        <v>3931</v>
+      </c>
+      <c r="L7">
+        <v>3685</v>
+      </c>
+      <c r="M7">
+        <v>864</v>
+      </c>
+      <c r="N7">
+        <v>22783</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8">
+        <v>4361</v>
+      </c>
+      <c r="D8">
+        <v>2808</v>
+      </c>
+      <c r="E8">
+        <v>422</v>
+      </c>
+      <c r="F8">
+        <v>339</v>
+      </c>
+      <c r="G8">
+        <v>373</v>
+      </c>
+      <c r="H8">
+        <v>545</v>
+      </c>
+      <c r="I8">
+        <v>639</v>
+      </c>
+      <c r="J8">
+        <v>23</v>
+      </c>
+      <c r="K8">
+        <v>4025</v>
+      </c>
+      <c r="L8">
+        <v>2428</v>
+      </c>
+      <c r="M8">
+        <v>496</v>
+      </c>
+      <c r="N8">
+        <v>16459</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9">
+        <v>7416</v>
+      </c>
+      <c r="D9">
+        <v>4794</v>
+      </c>
+      <c r="E9">
+        <v>696</v>
+      </c>
+      <c r="F9">
+        <v>485</v>
+      </c>
+      <c r="G9">
+        <v>770</v>
+      </c>
+      <c r="H9">
+        <v>684</v>
+      </c>
+      <c r="I9">
+        <v>1110</v>
+      </c>
+      <c r="J9">
+        <v>91</v>
+      </c>
+      <c r="K9">
+        <v>3392</v>
+      </c>
+      <c r="L9">
+        <v>1952</v>
+      </c>
+      <c r="M9">
+        <v>917</v>
+      </c>
+      <c r="N9">
+        <v>22305</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10">
+        <v>2526</v>
+      </c>
+      <c r="D10">
+        <v>1575</v>
+      </c>
+      <c r="E10">
+        <v>614</v>
+      </c>
+      <c r="F10">
+        <v>228</v>
+      </c>
+      <c r="G10">
+        <v>317</v>
+      </c>
+      <c r="H10">
+        <v>188</v>
+      </c>
+      <c r="I10">
+        <v>408</v>
+      </c>
+      <c r="J10">
+        <v>31</v>
+      </c>
+      <c r="K10">
+        <v>2555</v>
+      </c>
+      <c r="L10">
+        <v>1529</v>
+      </c>
+      <c r="M10">
+        <v>489</v>
+      </c>
+      <c r="N10">
+        <v>10461</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -3968,7 +6445,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -3981,300 +6458,300 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C3" s="14">
-        <v>0.10101</v>
+        <v>0.101</v>
       </c>
       <c r="D3" s="14">
         <v>0.07069397032923187</v>
       </c>
       <c r="E3" s="14">
-        <v>0.073787598718854</v>
+        <v>0.07099271034299512</v>
       </c>
       <c r="F3" s="15">
-        <v>0.730478862</v>
+        <v>0.702810642</v>
       </c>
       <c r="G3" s="24">
-        <v>-0.0272</v>
+        <v>-0.03</v>
       </c>
       <c r="H3" s="16">
-        <v>0.0030936283896221273</v>
+        <v>0.0002987400137632462</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C4" s="14">
-        <v>0.09754</v>
+        <v>0.0975</v>
       </c>
       <c r="D4" s="14">
         <v>0.12034112113750035</v>
       </c>
       <c r="E4" s="14">
-        <v>0.10340144743469554</v>
+        <v>0.10777447888386994</v>
       </c>
       <c r="F4" s="15">
-        <v>1.06014107</v>
+        <v>1.104977553</v>
       </c>
       <c r="G4" s="26">
-        <v>0.0059</v>
+        <v>0.0102</v>
       </c>
       <c r="H4" s="16">
-        <v>-0.016939673702804817</v>
+        <v>-0.012566642253630411</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C5" s="14">
-        <v>0.14619</v>
+        <v>0.1462</v>
       </c>
       <c r="D5" s="14">
         <v>0.06917375656428465</v>
       </c>
       <c r="E5" s="14">
-        <v>0.0633162305002398</v>
+        <v>0.07258157060724037</v>
       </c>
       <c r="F5" s="15">
-        <v>0.433104767</v>
+        <v>0.496482779</v>
       </c>
       <c r="G5" s="24">
-        <v>-0.0829</v>
+        <v>-0.0736</v>
       </c>
       <c r="H5" s="16">
-        <v>-0.0058575260640448545</v>
+        <v>0.0034078140429557174</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C6" s="14">
-        <v>0.14525</v>
+        <v>0.1453</v>
       </c>
       <c r="D6" s="14">
         <v>0.09625145593113094</v>
       </c>
       <c r="E6" s="14">
-        <v>0.09322771189157013</v>
+        <v>0.09161092562855482</v>
       </c>
       <c r="F6" s="15">
-        <v>0.641847568</v>
+        <v>0.630716309</v>
       </c>
       <c r="G6" s="24">
-        <v>-0.052</v>
+        <v>-0.0536</v>
       </c>
       <c r="H6" s="16">
-        <v>-0.003023744039560808</v>
+        <v>-0.004640530302576121</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C7" s="14">
-        <v>0.07317</v>
+        <v>0.0732</v>
       </c>
       <c r="D7" s="14">
         <v>0.14736642713492903</v>
       </c>
       <c r="E7" s="14">
-        <v>0.14565564742939358</v>
+        <v>0.13610286387634155</v>
       </c>
       <c r="F7" s="15">
-        <v>1.990588131</v>
+        <v>1.86003562</v>
       </c>
       <c r="G7" s="26">
-        <v>0.0725</v>
+        <v>0.0629</v>
       </c>
       <c r="H7" s="16">
-        <v>-0.001710779705535459</v>
+        <v>-0.011263563258587489</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C8" s="14">
-        <v>0.12271</v>
+        <v>0.1227</v>
       </c>
       <c r="D8" s="14">
         <v>0.13758176388323534</v>
       </c>
       <c r="E8" s="14">
-        <v>0.1647222135195124</v>
+        <v>0.1439108451458124</v>
       </c>
       <c r="F8" s="15">
-        <v>1.342339456</v>
+        <v>1.172745094</v>
       </c>
       <c r="G8" s="26">
-        <v>0.042</v>
+        <v>0.0212</v>
       </c>
       <c r="H8" s="16">
-        <v>0.02714044963627707</v>
+        <v>0.006329081262577058</v>
       </c>
       <c r="I8" s="27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C9" s="14">
-        <v>0.14039</v>
+        <v>0.1404</v>
       </c>
       <c r="D9" s="14">
         <v>0.12455435409051156</v>
       </c>
       <c r="E9" s="14">
-        <v>0.11899523064724865</v>
+        <v>0.1305021892076108</v>
       </c>
       <c r="F9" s="15">
-        <v>0.84761038</v>
+        <v>0.929574974</v>
       </c>
       <c r="G9" s="24">
-        <v>-0.0214</v>
+        <v>-0.0099</v>
       </c>
       <c r="H9" s="16">
-        <v>-0.005559123443262912</v>
+        <v>0.0059478351170992455</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C10" s="14">
-        <v>0.15611</v>
+        <v>0.1561</v>
       </c>
       <c r="D10" s="14">
         <v>0.1437287151936741</v>
       </c>
       <c r="E10" s="14">
-        <v>0.161265095519604</v>
+        <v>0.1624372792982213</v>
       </c>
       <c r="F10" s="15">
-        <v>1.033014434</v>
+        <v>1.040522878</v>
       </c>
       <c r="G10" s="26">
-        <v>0.0052</v>
+        <v>0.0063</v>
       </c>
       <c r="H10" s="16">
-        <v>0.017536380325929884</v>
+        <v>0.018708564104547187</v>
       </c>
       <c r="I10" s="27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C11" s="14">
-        <v>0.01763</v>
+        <v>0.0176</v>
       </c>
       <c r="D11" s="14">
         <v>0.09030843573550215</v>
       </c>
       <c r="E11" s="14">
-        <v>0.07562882433888192</v>
+        <v>0.08408713700935372</v>
       </c>
       <c r="F11" s="15">
-        <v>4.290709151</v>
+        <v>4.770580276</v>
       </c>
       <c r="G11" s="26">
-        <v>0.058</v>
+        <v>0.0665</v>
       </c>
       <c r="H11" s="16">
-        <v>-0.014679611396620232</v>
+        <v>-0.006221298726148433</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C12" s="20">
         <v>1</v>
@@ -4295,7 +6772,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -4307,7 +6784,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -4319,7 +6796,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -4337,486 +6814,486 @@
     </row>
     <row r="2" spans="1:14" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C3" s="12">
-        <v>3239.3333333333335</v>
+        <v>3277.6666666666665</v>
       </c>
       <c r="D3" s="12">
         <v>1712.1666666666667</v>
       </c>
       <c r="E3" s="12">
-        <v>4336.055555555556</v>
+        <v>4551.148148148149</v>
       </c>
       <c r="F3" s="12">
-        <v>1478.1666666666667</v>
+        <v>1518</v>
       </c>
       <c r="G3" s="12">
         <v>814.9166666666666</v>
       </c>
       <c r="H3" s="12">
-        <v>2712.962962962963</v>
+        <v>2766.7037037037035</v>
       </c>
       <c r="I3" s="12">
-        <v>2159.1666666666665</v>
+        <v>2298.222222222222</v>
       </c>
       <c r="J3" s="12">
         <v>2496.0833333333335</v>
       </c>
       <c r="K3" s="12">
-        <v>2697.6666666666665</v>
+        <v>3018.8395061728393</v>
       </c>
       <c r="L3" s="12">
-        <v>1093.6666666666667</v>
+        <v>1047.3333333333333</v>
       </c>
       <c r="M3" s="12">
         <v>946.6666666666666</v>
       </c>
       <c r="N3" s="12">
-        <v>1803.8148148148148</v>
+        <v>1774.358024691358</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C4" s="12">
-        <v>3916.6666666666665</v>
+        <v>4242.222222222223</v>
       </c>
       <c r="D4" s="12">
         <v>3317.5</v>
       </c>
       <c r="E4" s="12">
-        <v>4336.055555555556</v>
+        <v>4551.148148148149</v>
       </c>
       <c r="F4" s="12">
-        <v>1841</v>
+        <v>2126.3333333333335</v>
       </c>
       <c r="G4" s="12">
         <v>1365.3333333333333</v>
       </c>
       <c r="H4" s="12">
-        <v>2712.962962962963</v>
+        <v>2766.7037037037035</v>
       </c>
       <c r="I4" s="12">
-        <v>2900.5</v>
+        <v>3686.777777777778</v>
       </c>
       <c r="J4" s="12">
         <v>3579.0833333333335</v>
       </c>
       <c r="K4" s="12">
-        <v>2697.6666666666665</v>
+        <v>3018.8395061728393</v>
       </c>
       <c r="L4" s="12">
-        <v>1829.3333333333333</v>
+        <v>1672.6666666666667</v>
       </c>
       <c r="M4" s="12">
         <v>1292.3333333333333</v>
       </c>
       <c r="N4" s="12">
-        <v>1803.8148148148148</v>
+        <v>1774.358024691358</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C5" s="12">
-        <v>2575.3333333333335</v>
+        <v>3084.777777777778</v>
       </c>
       <c r="D5" s="12">
         <v>1968.75</v>
       </c>
       <c r="E5" s="12">
-        <v>4336.055555555556</v>
+        <v>4551.148148148149</v>
       </c>
       <c r="F5" s="12">
-        <v>1837.3333333333333</v>
+        <v>2069</v>
       </c>
       <c r="G5" s="12">
         <v>1203.5</v>
       </c>
       <c r="H5" s="12">
-        <v>2712.962962962963</v>
+        <v>2766.7037037037035</v>
       </c>
       <c r="I5" s="12">
-        <v>861.5</v>
+        <v>1259.111111111111</v>
       </c>
       <c r="J5" s="12">
         <v>950.1666666666666</v>
       </c>
       <c r="K5" s="12">
-        <v>2697.6666666666665</v>
+        <v>3018.8395061728393</v>
       </c>
       <c r="L5" s="12">
-        <v>505</v>
+        <v>665.4444444444445</v>
       </c>
       <c r="M5" s="12">
         <v>633.0833333333334</v>
       </c>
       <c r="N5" s="12">
-        <v>1803.8148148148148</v>
+        <v>1774.358024691358</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C6" s="12">
-        <v>3418.3333333333335</v>
+        <v>3632.222222222222</v>
       </c>
       <c r="D6" s="12">
         <v>2608.3333333333335</v>
       </c>
       <c r="E6" s="12">
-        <v>4336.055555555556</v>
+        <v>4551.148148148149</v>
       </c>
       <c r="F6" s="12">
-        <v>2040.5</v>
+        <v>2062</v>
       </c>
       <c r="G6" s="12">
         <v>1602.1666666666667</v>
       </c>
       <c r="H6" s="12">
-        <v>2712.962962962963</v>
+        <v>2766.7037037037035</v>
       </c>
       <c r="I6" s="12">
-        <v>1887.6666666666667</v>
+        <v>2118.222222222222</v>
       </c>
       <c r="J6" s="12">
         <v>1608.5</v>
       </c>
       <c r="K6" s="12">
-        <v>2697.6666666666665</v>
+        <v>3018.8395061728393</v>
       </c>
       <c r="L6" s="12">
-        <v>1286.3333333333333</v>
+        <v>1124.2222222222222</v>
       </c>
       <c r="M6" s="12">
         <v>721.9166666666666</v>
       </c>
       <c r="N6" s="12">
-        <v>1803.8148148148148</v>
+        <v>1774.358024691358</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C7" s="12">
-        <v>5480.833333333333</v>
+        <v>5458.444444444444</v>
       </c>
       <c r="D7" s="12">
         <v>4024</v>
       </c>
       <c r="E7" s="12">
-        <v>4336.055555555556</v>
+        <v>4551.148148148149</v>
       </c>
       <c r="F7" s="12">
-        <v>4201</v>
+        <v>4054.4444444444443</v>
       </c>
       <c r="G7" s="12">
         <v>2640.0833333333335</v>
       </c>
       <c r="H7" s="12">
-        <v>2712.962962962963</v>
+        <v>2766.7037037037035</v>
       </c>
       <c r="I7" s="12">
-        <v>2566.8333333333335</v>
+        <v>2507.4444444444443</v>
       </c>
       <c r="J7" s="12">
         <v>2581</v>
       </c>
       <c r="K7" s="12">
-        <v>2697.6666666666665</v>
+        <v>3018.8395061728393</v>
       </c>
       <c r="L7" s="12">
-        <v>1925.5</v>
+        <v>1799.3333333333333</v>
       </c>
       <c r="M7" s="12">
         <v>1404</v>
       </c>
       <c r="N7" s="12">
-        <v>1803.8148148148148</v>
+        <v>1774.358024691358</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C8" s="12">
-        <v>6090.833333333333</v>
+        <v>5549.666666666667</v>
       </c>
       <c r="D8" s="12">
         <v>3800.4166666666665</v>
       </c>
       <c r="E8" s="12">
-        <v>4336.055555555556</v>
+        <v>4551.148148148149</v>
       </c>
       <c r="F8" s="12">
-        <v>3842.8333333333335</v>
+        <v>3388.3333333333335</v>
       </c>
       <c r="G8" s="12">
         <v>2045.25</v>
       </c>
       <c r="H8" s="12">
-        <v>2712.962962962963</v>
+        <v>2766.7037037037035</v>
       </c>
       <c r="I8" s="12">
-        <v>3931.3333333333335</v>
+        <v>3548.1111111111113</v>
       </c>
       <c r="J8" s="12">
         <v>3700.8333333333335</v>
       </c>
       <c r="K8" s="12">
-        <v>2697.6666666666665</v>
+        <v>3018.8395061728393</v>
       </c>
       <c r="L8" s="12">
-        <v>3685.1666666666665</v>
+        <v>3049.4444444444443</v>
       </c>
       <c r="M8" s="12">
         <v>1821.9166666666667</v>
       </c>
       <c r="N8" s="12">
-        <v>1803.8148148148148</v>
+        <v>1774.358024691358</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C9" s="12">
-        <v>4361.333333333333</v>
+        <v>5217.777777777777</v>
       </c>
       <c r="D9" s="12">
         <v>3766.5833333333335</v>
       </c>
       <c r="E9" s="12">
-        <v>4336.055555555556</v>
+        <v>4551.148148148149</v>
       </c>
       <c r="F9" s="12">
-        <v>2807.8333333333335</v>
+        <v>3327</v>
       </c>
       <c r="G9" s="12">
         <v>1919.8333333333333</v>
       </c>
       <c r="H9" s="12">
-        <v>2712.962962962963</v>
+        <v>2766.7037037037035</v>
       </c>
       <c r="I9" s="12">
-        <v>4025</v>
+        <v>4922.444444444444</v>
       </c>
       <c r="J9" s="12">
         <v>3422.0833333333335</v>
       </c>
       <c r="K9" s="12">
-        <v>2697.6666666666665</v>
+        <v>3018.8395061728393</v>
       </c>
       <c r="L9" s="12">
-        <v>2428.3333333333335</v>
+        <v>2552.5555555555557</v>
       </c>
       <c r="M9" s="12">
         <v>1527.75</v>
       </c>
       <c r="N9" s="12">
-        <v>1803.8148148148148</v>
+        <v>1774.358024691358</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C10" s="12">
-        <v>7415.666666666667</v>
+        <v>7890</v>
       </c>
       <c r="D10" s="12">
         <v>4877</v>
       </c>
       <c r="E10" s="12">
-        <v>4336.055555555556</v>
+        <v>4551.148148148149</v>
       </c>
       <c r="F10" s="12">
-        <v>4793.5</v>
+        <v>4469.444444444444</v>
       </c>
       <c r="G10" s="12">
         <v>1966.8333333333333</v>
       </c>
       <c r="H10" s="12">
-        <v>2712.962962962963</v>
+        <v>2766.7037037037035</v>
       </c>
       <c r="I10" s="12">
-        <v>3392.1666666666665</v>
+        <v>3873.1111111111113</v>
       </c>
       <c r="J10" s="12">
         <v>3588.4166666666665</v>
       </c>
       <c r="K10" s="12">
-        <v>2697.6666666666665</v>
+        <v>3018.8395061728393</v>
       </c>
       <c r="L10" s="12">
-        <v>1952</v>
+        <v>2182.1111111111113</v>
       </c>
       <c r="M10" s="12">
         <v>1627.3333333333333</v>
       </c>
       <c r="N10" s="12">
-        <v>1803.8148148148148</v>
+        <v>1774.358024691358</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C11" s="12">
-        <v>2526.1666666666665</v>
+        <v>2607.5555555555557</v>
       </c>
       <c r="D11" s="12">
         <v>1816.3333333333333</v>
       </c>
       <c r="E11" s="12">
-        <v>4336.055555555556</v>
+        <v>4551.148148148149</v>
       </c>
       <c r="F11" s="12">
-        <v>1574.5</v>
+        <v>1885.7777777777778</v>
       </c>
       <c r="G11" s="12">
         <v>1216.5833333333333</v>
       </c>
       <c r="H11" s="12">
-        <v>2712.962962962963</v>
+        <v>2766.7037037037035</v>
       </c>
       <c r="I11" s="12">
-        <v>2554.8333333333335</v>
+        <v>2956.1111111111113</v>
       </c>
       <c r="J11" s="12">
         <v>2864.3333333333335</v>
       </c>
       <c r="K11" s="12">
-        <v>2697.6666666666665</v>
+        <v>3018.8395061728393</v>
       </c>
       <c r="L11" s="12">
-        <v>1529</v>
+        <v>1876.111111111111</v>
       </c>
       <c r="M11" s="12">
         <v>1632.1666666666667</v>
       </c>
       <c r="N11" s="12">
-        <v>1803.8148148148148</v>
+        <v>1774.358024691358</v>
       </c>
     </row>
     <row r="12" spans="1:14" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C12" s="18">
-        <v>39024.5</v>
+        <v>40960.333333333336</v>
       </c>
       <c r="D12" s="18">
         <v>27891.083333333332</v>
       </c>
       <c r="E12" s="18">
-        <v>4336.055555555556</v>
+        <v>4551.148148148149</v>
       </c>
       <c r="F12" s="18">
-        <v>24416.666666666668</v>
+        <v>24900.333333333332</v>
       </c>
       <c r="G12" s="18">
         <v>14774.5</v>
       </c>
       <c r="H12" s="18">
-        <v>2712.962962962963</v>
+        <v>2766.7037037037035</v>
       </c>
       <c r="I12" s="18">
-        <v>24279</v>
+        <v>27169.555555555555</v>
       </c>
       <c r="J12" s="18">
         <v>24790.5</v>
       </c>
       <c r="K12" s="18">
-        <v>2697.6666666666665</v>
+        <v>3018.8395061728393</v>
       </c>
       <c r="L12" s="18">
-        <v>16234.333333333334</v>
+        <v>15969.222222222223</v>
       </c>
       <c r="M12" s="18">
         <v>11607.166666666666</v>
       </c>
       <c r="N12" s="18">
-        <v>1803.8148148148148</v>
+        <v>1774.358024691358</v>
       </c>
     </row>
   </sheetData>
@@ -4828,7 +7305,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -4840,7 +7317,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -4861,585 +7338,585 @@
     </row>
     <row r="2" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C3" s="12">
-        <v>254.5</v>
+        <v>222.77777777777777</v>
       </c>
       <c r="D3" s="12">
         <v>176.75</v>
       </c>
       <c r="E3" s="12">
-        <v>481.6296296296297</v>
+        <v>407.4567901234568</v>
       </c>
       <c r="F3" s="12">
-        <v>376.6666666666667</v>
+        <v>488.77777777777777</v>
       </c>
       <c r="G3" s="12">
         <v>283.25</v>
       </c>
       <c r="H3" s="12">
-        <v>655.4444444444445</v>
+        <v>879.1234567901234</v>
       </c>
       <c r="I3" s="12">
-        <v>315.8333333333333</v>
+        <v>333.3333333333333</v>
       </c>
       <c r="J3" s="12">
         <v>307.75</v>
       </c>
       <c r="K3" s="12">
-        <v>519.6481481481482</v>
+        <v>567.5185185185186</v>
       </c>
       <c r="L3" s="12">
-        <v>356</v>
+        <v>409</v>
       </c>
       <c r="M3" s="12">
         <v>307.6666666666667</v>
       </c>
       <c r="N3" s="12">
-        <v>835.4259259259259</v>
+        <v>1119.1728395061727</v>
       </c>
       <c r="O3" s="12">
-        <v>58.333333333333336</v>
+        <v>43.888888888888886</v>
       </c>
       <c r="P3" s="12">
         <v>34.75</v>
       </c>
       <c r="Q3" s="12">
-        <v>80.14814814814815</v>
+        <v>75.02469135802468</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C4" s="12">
-        <v>429.6666666666667</v>
+        <v>356.22222222222223</v>
       </c>
       <c r="D4" s="12">
         <v>409.4166666666667</v>
       </c>
       <c r="E4" s="12">
-        <v>481.6296296296297</v>
+        <v>407.4567901234568</v>
       </c>
       <c r="F4" s="12">
-        <v>742.8333333333334</v>
+        <v>971.1111111111111</v>
       </c>
       <c r="G4" s="12">
         <v>688.25</v>
       </c>
       <c r="H4" s="12">
-        <v>655.4444444444445</v>
+        <v>879.1234567901234</v>
       </c>
       <c r="I4" s="12">
-        <v>595.3333333333334</v>
+        <v>621.4444444444445</v>
       </c>
       <c r="J4" s="12">
         <v>747.8333333333334</v>
       </c>
       <c r="K4" s="12">
-        <v>519.6481481481482</v>
+        <v>567.5185185185186</v>
       </c>
       <c r="L4" s="12">
-        <v>776.6666666666666</v>
+        <v>982.5555555555555</v>
       </c>
       <c r="M4" s="12">
         <v>589.4166666666666</v>
       </c>
       <c r="N4" s="12">
-        <v>835.4259259259259</v>
+        <v>1119.1728395061727</v>
       </c>
       <c r="O4" s="12">
-        <v>64.5</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="P4" s="12">
         <v>67.25</v>
       </c>
       <c r="Q4" s="12">
-        <v>80.14814814814815</v>
+        <v>75.02469135802468</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C5" s="12">
-        <v>429</v>
+        <v>423.6666666666667</v>
       </c>
       <c r="D5" s="12">
         <v>281</v>
       </c>
       <c r="E5" s="12">
-        <v>481.6296296296297</v>
+        <v>407.4567901234568</v>
       </c>
       <c r="F5" s="12">
-        <v>498.3333333333333</v>
+        <v>683.6666666666666</v>
       </c>
       <c r="G5" s="12">
         <v>520.0833333333334</v>
       </c>
       <c r="H5" s="12">
-        <v>655.4444444444445</v>
+        <v>879.1234567901234</v>
       </c>
       <c r="I5" s="12">
-        <v>373.3333333333333</v>
+        <v>419.22222222222223</v>
       </c>
       <c r="J5" s="12">
         <v>669.9166666666666</v>
       </c>
       <c r="K5" s="12">
-        <v>519.6481481481482</v>
+        <v>567.5185185185186</v>
       </c>
       <c r="L5" s="12">
-        <v>635.5</v>
+        <v>1113.5555555555557</v>
       </c>
       <c r="M5" s="12">
         <v>462.5833333333333</v>
       </c>
       <c r="N5" s="12">
-        <v>835.4259259259259</v>
+        <v>1119.1728395061727</v>
       </c>
       <c r="O5" s="12">
-        <v>93.5</v>
+        <v>81.22222222222223</v>
       </c>
       <c r="P5" s="12">
         <v>122.75</v>
       </c>
       <c r="Q5" s="12">
-        <v>80.14814814814815</v>
+        <v>75.02469135802468</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C6" s="12">
-        <v>710</v>
+        <v>560.7777777777778</v>
       </c>
       <c r="D6" s="12">
         <v>510.4166666666667</v>
       </c>
       <c r="E6" s="12">
-        <v>481.6296296296297</v>
+        <v>407.4567901234568</v>
       </c>
       <c r="F6" s="12">
-        <v>699.3333333333334</v>
+        <v>954.7777777777778</v>
       </c>
       <c r="G6" s="12">
         <v>692.75</v>
       </c>
       <c r="H6" s="12">
-        <v>655.4444444444445</v>
+        <v>879.1234567901234</v>
       </c>
       <c r="I6" s="12">
-        <v>550</v>
+        <v>599</v>
       </c>
       <c r="J6" s="12">
         <v>860.6666666666666</v>
       </c>
       <c r="K6" s="12">
-        <v>519.6481481481482</v>
+        <v>567.5185185185186</v>
       </c>
       <c r="L6" s="12">
-        <v>1057.1666666666667</v>
+        <v>1240</v>
       </c>
       <c r="M6" s="12">
         <v>702.4166666666666</v>
       </c>
       <c r="N6" s="12">
-        <v>835.4259259259259</v>
+        <v>1119.1728395061727</v>
       </c>
       <c r="O6" s="12">
-        <v>230.16666666666666</v>
+        <v>215.88888888888889</v>
       </c>
       <c r="P6" s="12">
         <v>214.16666666666666</v>
       </c>
       <c r="Q6" s="12">
-        <v>80.14814814814815</v>
+        <v>75.02469135802468</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C7" s="12">
-        <v>624</v>
+        <v>496.1111111111111</v>
       </c>
       <c r="D7" s="12">
         <v>420</v>
       </c>
       <c r="E7" s="12">
-        <v>481.6296296296297</v>
+        <v>407.4567901234568</v>
       </c>
       <c r="F7" s="12">
-        <v>1037</v>
+        <v>1302.6666666666667</v>
       </c>
       <c r="G7" s="12">
         <v>1143.6666666666667</v>
       </c>
       <c r="H7" s="12">
-        <v>655.4444444444445</v>
+        <v>879.1234567901234</v>
       </c>
       <c r="I7" s="12">
-        <v>904</v>
+        <v>948.6666666666666</v>
       </c>
       <c r="J7" s="12">
         <v>1220.9166666666667</v>
       </c>
       <c r="K7" s="12">
-        <v>519.6481481481482</v>
+        <v>567.5185185185186</v>
       </c>
       <c r="L7" s="12">
-        <v>1298.3333333333333</v>
+        <v>1562.4444444444443</v>
       </c>
       <c r="M7" s="12">
         <v>913.0833333333334</v>
       </c>
       <c r="N7" s="12">
-        <v>835.4259259259259</v>
+        <v>1119.1728395061727</v>
       </c>
       <c r="O7" s="12">
-        <v>70.16666666666667</v>
+        <v>65.88888888888889</v>
       </c>
       <c r="P7" s="12">
         <v>154.66666666666666</v>
       </c>
       <c r="Q7" s="12">
-        <v>80.14814814814815</v>
+        <v>75.02469135802468</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C8" s="12">
-        <v>836</v>
+        <v>646.5555555555555</v>
       </c>
       <c r="D8" s="12">
         <v>413.4166666666667</v>
       </c>
       <c r="E8" s="12">
-        <v>481.6296296296297</v>
+        <v>407.4567901234568</v>
       </c>
       <c r="F8" s="12">
-        <v>1084.8333333333333</v>
+        <v>1314.2222222222222</v>
       </c>
       <c r="G8" s="12">
         <v>733.25</v>
       </c>
       <c r="H8" s="12">
-        <v>655.4444444444445</v>
+        <v>879.1234567901234</v>
       </c>
       <c r="I8" s="12">
-        <v>521</v>
+        <v>528.8888888888889</v>
       </c>
       <c r="J8" s="12">
         <v>592.6666666666666</v>
       </c>
       <c r="K8" s="12">
-        <v>519.6481481481482</v>
+        <v>567.5185185185186</v>
       </c>
       <c r="L8" s="12">
-        <v>1238.3333333333333</v>
+        <v>1647.3333333333333</v>
       </c>
       <c r="M8" s="12">
         <v>657.9166666666666</v>
       </c>
       <c r="N8" s="12">
-        <v>835.4259259259259</v>
+        <v>1119.1728395061727</v>
       </c>
       <c r="O8" s="12">
-        <v>59.666666666666664</v>
+        <v>54.44444444444444</v>
       </c>
       <c r="P8" s="12">
         <v>60.833333333333336</v>
       </c>
       <c r="Q8" s="12">
-        <v>80.14814814814815</v>
+        <v>75.02469135802468</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C9" s="12">
-        <v>338.5</v>
+        <v>325.1111111111111</v>
       </c>
       <c r="D9" s="12">
         <v>234.66666666666666</v>
       </c>
       <c r="E9" s="12">
-        <v>481.6296296296297</v>
+        <v>407.4567901234568</v>
       </c>
       <c r="F9" s="12">
-        <v>373.3333333333333</v>
+        <v>447</v>
       </c>
       <c r="G9" s="12">
         <v>444.5833333333333</v>
       </c>
       <c r="H9" s="12">
-        <v>655.4444444444445</v>
+        <v>879.1234567901234</v>
       </c>
       <c r="I9" s="12">
-        <v>544.8333333333334</v>
+        <v>518.4444444444445</v>
       </c>
       <c r="J9" s="12">
         <v>674.0833333333334</v>
       </c>
       <c r="K9" s="12">
-        <v>519.6481481481482</v>
+        <v>567.5185185185186</v>
       </c>
       <c r="L9" s="12">
-        <v>638.6666666666666</v>
+        <v>846.5555555555555</v>
       </c>
       <c r="M9" s="12">
         <v>508.75</v>
       </c>
       <c r="N9" s="12">
-        <v>835.4259259259259</v>
+        <v>1119.1728395061727</v>
       </c>
       <c r="O9" s="12">
-        <v>22.833333333333332</v>
+        <v>31.666666666666668</v>
       </c>
       <c r="P9" s="12">
         <v>40.083333333333336</v>
       </c>
       <c r="Q9" s="12">
-        <v>80.14814814814815</v>
+        <v>75.02469135802468</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C10" s="12">
-        <v>484.6666666666667</v>
+        <v>435.3333333333333</v>
       </c>
       <c r="D10" s="12">
         <v>356.8333333333333</v>
       </c>
       <c r="E10" s="12">
-        <v>481.6296296296297</v>
+        <v>407.4567901234568</v>
       </c>
       <c r="F10" s="12">
-        <v>769.6666666666666</v>
+        <v>1017.3333333333334</v>
       </c>
       <c r="G10" s="12">
         <v>519.6666666666666</v>
       </c>
       <c r="H10" s="12">
-        <v>655.4444444444445</v>
+        <v>879.1234567901234</v>
       </c>
       <c r="I10" s="12">
-        <v>684.3333333333334</v>
+        <v>833.6666666666666</v>
       </c>
       <c r="J10" s="12">
         <v>705.6666666666666</v>
       </c>
       <c r="K10" s="12">
-        <v>519.6481481481482</v>
+        <v>567.5185185185186</v>
       </c>
       <c r="L10" s="12">
-        <v>1109.8333333333333</v>
+        <v>1516.7777777777778</v>
       </c>
       <c r="M10" s="12">
         <v>732</v>
       </c>
       <c r="N10" s="12">
-        <v>835.4259259259259</v>
+        <v>1119.1728395061727</v>
       </c>
       <c r="O10" s="12">
-        <v>91.33333333333333</v>
+        <v>96.77777777777777</v>
       </c>
       <c r="P10" s="12">
         <v>95.83333333333333</v>
       </c>
       <c r="Q10" s="12">
-        <v>80.14814814814815</v>
+        <v>75.02469135802468</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C11" s="12">
-        <v>228.33333333333334</v>
+        <v>200.55555555555554</v>
       </c>
       <c r="D11" s="12">
         <v>270.8333333333333</v>
       </c>
       <c r="E11" s="12">
-        <v>481.6296296296297</v>
+        <v>407.4567901234568</v>
       </c>
       <c r="F11" s="12">
-        <v>317</v>
+        <v>732.5555555555555</v>
       </c>
       <c r="G11" s="12">
         <v>410.9166666666667</v>
       </c>
       <c r="H11" s="12">
-        <v>655.4444444444445</v>
+        <v>879.1234567901234</v>
       </c>
       <c r="I11" s="12">
-        <v>188.16666666666666</v>
+        <v>305</v>
       </c>
       <c r="J11" s="12">
         <v>423.75</v>
       </c>
       <c r="K11" s="12">
-        <v>519.6481481481482</v>
+        <v>567.5185185185186</v>
       </c>
       <c r="L11" s="12">
-        <v>408.3333333333333</v>
+        <v>754.3333333333334</v>
       </c>
       <c r="M11" s="12">
         <v>386.9166666666667</v>
       </c>
       <c r="N11" s="12">
-        <v>835.4259259259259</v>
+        <v>1119.1728395061727</v>
       </c>
       <c r="O11" s="12">
-        <v>30.833333333333332</v>
+        <v>34.77777777777778</v>
       </c>
       <c r="P11" s="12">
         <v>42.333333333333336</v>
       </c>
       <c r="Q11" s="12">
-        <v>80.14814814814815</v>
+        <v>75.02469135802468</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C12" s="18">
-        <v>4334.666666666667</v>
+        <v>3667.1111111111113</v>
       </c>
       <c r="D12" s="18">
         <v>3073.3333333333335</v>
       </c>
       <c r="E12" s="18">
-        <v>481.6296296296297</v>
+        <v>407.4567901234568</v>
       </c>
       <c r="F12" s="18">
-        <v>5899</v>
+        <v>7912.111111111111</v>
       </c>
       <c r="G12" s="18">
         <v>5436.416666666667</v>
       </c>
       <c r="H12" s="18">
-        <v>655.4444444444445</v>
+        <v>879.1234567901234</v>
       </c>
       <c r="I12" s="18">
-        <v>4676.833333333333</v>
+        <v>5107.666666666667</v>
       </c>
       <c r="J12" s="18">
         <v>6203.25</v>
       </c>
       <c r="K12" s="18">
-        <v>519.6481481481482</v>
+        <v>567.5185185185186</v>
       </c>
       <c r="L12" s="18">
-        <v>7518.833333333333</v>
+        <v>10072.555555555555</v>
       </c>
       <c r="M12" s="18">
         <v>5260.75</v>
       </c>
       <c r="N12" s="18">
-        <v>835.4259259259259</v>
+        <v>1119.1728395061727</v>
       </c>
       <c r="O12" s="18">
-        <v>721.3333333333334</v>
+        <v>675.2222222222222</v>
       </c>
       <c r="P12" s="18">
         <v>832.6666666666666</v>
       </c>
       <c r="Q12" s="18">
-        <v>80.14814814814815</v>
+        <v>75.02469135802468</v>
       </c>
     </row>
   </sheetData>
@@ -5451,7 +7928,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -5463,7 +7940,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -5474,27 +7951,27 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E3" s="29">
-        <v>0.5011</v>
+        <v>0.577093334529738</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G3" s="30">
-        <v>0.33785</v>
+        <v>0.3954530615863907</v>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B5" s="31"/>
       <c r="C5" s="31"/>
@@ -5505,269 +7982,269 @@
     </row>
     <row r="7" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B8" s="12">
         <v>4877</v>
       </c>
       <c r="C8" s="12">
-        <v>7415.666666666667</v>
+        <v>7890</v>
       </c>
       <c r="D8" s="32">
-        <v>2538.666666666667</v>
+        <v>3013</v>
       </c>
       <c r="E8" s="33">
-        <v>0.520538582461896</v>
+        <v>0.6177978265327044</v>
       </c>
       <c r="F8" s="33">
-        <v>0.3992</v>
+        <v>0.4685816554275113</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B9" s="12">
         <v>1966.8333333333333</v>
       </c>
       <c r="C9" s="12">
-        <v>4793.5</v>
+        <v>4469.444444444444</v>
       </c>
       <c r="D9" s="32">
-        <v>2826.666666666667</v>
+        <v>2502.6111111111113</v>
       </c>
       <c r="E9" s="33">
-        <v>1.4371663418354377</v>
+        <v>1.2724062932519842</v>
       </c>
       <c r="F9" s="33">
-        <v>0.6526</v>
+        <v>0.685358782587115</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B10" s="12">
         <v>389.75</v>
       </c>
       <c r="C10" s="12">
-        <v>695.5</v>
+        <v>507.1111111111111</v>
       </c>
       <c r="D10" s="32">
-        <v>305.75</v>
+        <v>117.36111111111109</v>
       </c>
       <c r="E10" s="33">
-        <v>0.7844772289929443</v>
+        <v>0.30111895089444785</v>
       </c>
       <c r="F10" s="33">
-        <v>0.5185</v>
+        <v>0.11069489556414336</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B11" s="12">
         <v>356.8333333333333</v>
       </c>
       <c r="C11" s="12">
-        <v>484.6666666666667</v>
+        <v>435.3333333333333</v>
       </c>
       <c r="D11" s="32">
-        <v>127.83333333333337</v>
+        <v>78.5</v>
       </c>
       <c r="E11" s="33">
-        <v>0.35824381130312943</v>
+        <v>0.2199906585707614</v>
       </c>
       <c r="F11" s="33">
-        <v>0.4104</v>
-      </c>
-      <c r="G11" s="34" t="s">
-        <v>143</v>
+        <v>0.19320318148951565</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B12" s="12">
         <v>519.6666666666666</v>
       </c>
       <c r="C12" s="12">
-        <v>769.6666666666666</v>
+        <v>1017.3333333333334</v>
       </c>
       <c r="D12" s="32">
-        <v>250</v>
+        <v>497.66666666666674</v>
       </c>
       <c r="E12" s="33">
-        <v>0.4810776138550352</v>
+        <v>0.957665169980757</v>
       </c>
       <c r="F12" s="33">
-        <v>0.0851</v>
+        <v>0.45539085692679504</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B13" s="12">
         <v>705.6666666666666</v>
       </c>
       <c r="C13" s="12">
-        <v>684.3333333333334</v>
+        <v>833.6666666666666</v>
       </c>
       <c r="D13" s="32">
-        <v>-21.333333333333258</v>
+        <v>128</v>
       </c>
       <c r="E13" s="33">
-        <v>-0.030231459612659273</v>
+        <v>0.18138875767595652</v>
       </c>
       <c r="F13" s="33">
-        <v>-0.2461</v>
+        <v>-0.17661440911350224</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B14" s="12">
         <v>732</v>
       </c>
       <c r="C14" s="12">
-        <v>1109.8333333333333</v>
+        <v>1516.7777777777778</v>
       </c>
       <c r="D14" s="32">
-        <v>377.83333333333326</v>
+        <v>784.7777777777778</v>
       </c>
       <c r="E14" s="33">
-        <v>0.5161657559198543</v>
+        <v>1.0721007893139043</v>
       </c>
       <c r="F14" s="33">
-        <v>0.4292</v>
+        <v>0.9146615131978435</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B15" s="12">
         <v>95.83333333333333</v>
       </c>
       <c r="C15" s="12">
-        <v>91.33333333333333</v>
+        <v>96.77777777777777</v>
       </c>
       <c r="D15" s="32">
-        <v>-4.5</v>
+        <v>0.9444444444444429</v>
       </c>
       <c r="E15" s="33">
-        <v>-0.04695652173913045</v>
+        <v>0.009855072463768044</v>
       </c>
       <c r="F15" s="33">
-        <v>-0.1337</v>
+        <v>-0.1890846010141447</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B16" s="12">
         <v>3588.4166666666665</v>
       </c>
       <c r="C16" s="12">
-        <v>3392.1666666666665</v>
+        <v>3873.1111111111113</v>
       </c>
       <c r="D16" s="32">
-        <v>-196.25</v>
+        <v>284.6944444444448</v>
       </c>
       <c r="E16" s="33">
-        <v>-0.05468985857272246</v>
+        <v>0.07933706447442779</v>
       </c>
       <c r="F16" s="33">
-        <v>-0.0206</v>
+        <v>0.09596642082876716</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B17" s="12">
         <v>1627.3333333333333</v>
       </c>
       <c r="C17" s="12">
-        <v>1952</v>
+        <v>2182.1111111111113</v>
       </c>
       <c r="D17" s="32">
-        <v>324.66666666666674</v>
+        <v>554.777777777778</v>
       </c>
       <c r="E17" s="33">
-        <v>0.19950839819746014</v>
+        <v>0.3409121944558242</v>
       </c>
       <c r="F17" s="33">
-        <v>0.3986</v>
+        <v>0.37580709236152</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B18" s="12">
         <v>0</v>
       </c>
       <c r="C18" s="12">
-        <v>916.5</v>
+        <v>612.8888888888889</v>
       </c>
       <c r="D18" s="32">
-        <v>916.5</v>
+        <v>612.8888888888889</v>
       </c>
       <c r="E18" s="33">
         <v>1</v>
@@ -5776,30 +8253,30 @@
         <v>1</v>
       </c>
       <c r="G18" s="27" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B19" s="18">
         <v>14859.333333333334</v>
       </c>
       <c r="C19" s="18">
-        <v>22305.166666666668</v>
+        <v>23434.555555555555</v>
       </c>
       <c r="D19" s="35">
-        <v>7445.833333333334</v>
+        <v>8575.22222222222</v>
       </c>
       <c r="E19" s="36">
-        <v>0.5011</v>
+        <v>0.577093334529738</v>
       </c>
       <c r="F19" s="36">
-        <v>0.33785</v>
+        <v>0.3954530615863907</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -5810,646 +8287,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-    </row>
-    <row r="2" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="B3" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="C3" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="D3" s="38">
-        <v>103384.58333333333</v>
-      </c>
-      <c r="E3" s="38">
-        <v>138313.66666666666</v>
-      </c>
-      <c r="F3" s="39">
-        <v>0.33785</v>
-      </c>
-      <c r="G3" s="37" t="s">
-        <v>155</v>
-      </c>
-      <c r="H3" s="37" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" s="12">
-        <v>14224</v>
-      </c>
-      <c r="E4" s="12">
-        <v>22783</v>
-      </c>
-      <c r="F4" s="40">
-        <v>0.6018</v>
-      </c>
-      <c r="G4" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="H4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" s="12">
-        <v>14859</v>
-      </c>
-      <c r="E5" s="12">
-        <v>22305</v>
-      </c>
-      <c r="F5" s="40">
-        <v>0.5011</v>
-      </c>
-      <c r="G5" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="H5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D6" s="12">
-        <v>7309</v>
-      </c>
-      <c r="E6" s="12">
-        <v>10206</v>
-      </c>
-      <c r="F6" s="40">
-        <v>0.3964</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="H6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" s="12">
-        <v>15235</v>
-      </c>
-      <c r="E7" s="12">
-        <v>20146</v>
-      </c>
-      <c r="F7" s="41">
-        <v>0.3223</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="H7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="12">
-        <v>9951</v>
-      </c>
-      <c r="E8" s="12">
-        <v>12895</v>
-      </c>
-      <c r="F8" s="41">
-        <v>0.2958</v>
-      </c>
-      <c r="G8" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="H8" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" s="12">
-        <v>12877</v>
-      </c>
-      <c r="E9" s="12">
-        <v>16459</v>
-      </c>
-      <c r="F9" s="41">
-        <v>0.2781</v>
-      </c>
-      <c r="G9" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="H9" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>162</v>
-      </c>
-      <c r="D10" s="12">
-        <v>7152</v>
-      </c>
-      <c r="E10" s="12">
-        <v>8758</v>
-      </c>
-      <c r="F10" s="41">
-        <v>0.2246</v>
-      </c>
-      <c r="G10" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="H10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="12">
-        <v>12441</v>
-      </c>
-      <c r="E11" s="12">
-        <v>14302</v>
-      </c>
-      <c r="F11" s="41">
-        <v>0.1495</v>
-      </c>
-      <c r="G11" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="H11" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" s="12">
-        <v>9337</v>
-      </c>
-      <c r="E12" s="12">
-        <v>10461</v>
-      </c>
-      <c r="F12" s="41">
-        <v>0.1204</v>
-      </c>
-      <c r="G12" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="H12" t="s">
-        <v>161</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-    </row>
-    <row r="2" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="B3" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="C3" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="D3" s="38">
-        <v>27891.083333333332</v>
-      </c>
-      <c r="E3" s="38">
-        <v>39024.5</v>
-      </c>
-      <c r="F3" s="39">
-        <v>0.3992</v>
-      </c>
-      <c r="G3" s="37" t="s">
-        <v>155</v>
-      </c>
-      <c r="H3" s="37" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>159</v>
-      </c>
-      <c r="D4" s="12">
-        <v>1712</v>
-      </c>
-      <c r="E4" s="12">
-        <v>3239</v>
-      </c>
-      <c r="F4" s="40">
-        <v>0.8919</v>
-      </c>
-      <c r="G4" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="H4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" s="12">
-        <v>3800</v>
-      </c>
-      <c r="E5" s="12">
-        <v>6091</v>
-      </c>
-      <c r="F5" s="40">
-        <v>0.6027</v>
-      </c>
-      <c r="G5" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="H5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" s="12">
-        <v>4877</v>
-      </c>
-      <c r="E6" s="12">
-        <v>7416</v>
-      </c>
-      <c r="F6" s="40">
-        <v>0.5205</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="H6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" s="12">
-        <v>1816</v>
-      </c>
-      <c r="E7" s="12">
-        <v>2526</v>
-      </c>
-      <c r="F7" s="41">
-        <v>0.3908</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="H7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" s="12">
-        <v>4024</v>
-      </c>
-      <c r="E8" s="12">
-        <v>5481</v>
-      </c>
-      <c r="F8" s="41">
-        <v>0.362</v>
-      </c>
-      <c r="G8" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="H8" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="12">
-        <v>2608</v>
-      </c>
-      <c r="E9" s="12">
-        <v>3418</v>
-      </c>
-      <c r="F9" s="41">
-        <v>0.3105</v>
-      </c>
-      <c r="G9" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="H9" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>162</v>
-      </c>
-      <c r="D10" s="12">
-        <v>1969</v>
-      </c>
-      <c r="E10" s="12">
-        <v>2575</v>
-      </c>
-      <c r="F10" s="41">
-        <v>0.3081</v>
-      </c>
-      <c r="G10" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="H10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="12">
-        <v>3318</v>
-      </c>
-      <c r="E11" s="12">
-        <v>3917</v>
-      </c>
-      <c r="F11" s="41">
-        <v>0.1806</v>
-      </c>
-      <c r="G11" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="H11" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12" s="12">
-        <v>3767</v>
-      </c>
-      <c r="E12" s="12">
-        <v>4361</v>
-      </c>
-      <c r="F12" s="41">
-        <v>0.1579</v>
-      </c>
-      <c r="G12" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="H12" t="s">
-        <v>161</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
 </file>
--- a/Egy_Nutri_Sales_Analysis_Template.xlsx
+++ b/Egy_Nutri_Sales_Analysis_Template.xlsx
@@ -19,14 +19,14 @@
     <sheet sheetId="13" name="Slide8_PediaStart1_Ranking" state="visible" r:id="rId16"/>
     <sheet sheetId="14" name="Slide9_PediaStart2_Ranking" state="visible" r:id="rId17"/>
     <sheet sheetId="15" name="Slide10_Quadrant_Matrix" state="visible" r:id="rId18"/>
-    <sheet sheetId="16" name="11-Q3 vs H1 Rep Velocity" state="visible" r:id="rId19"/>
+    <sheet sheetId="16" name="11-3-Horizon Rep Velocity" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="261">
   <si>
     <t>EGY NUTRI. - BUSINESS REVIEW &amp; SALES ANALYSIS MODEL</t>
   </si>
@@ -619,25 +619,34 @@
     <t>COMPANY STAR: Heavy volume, high growth exceeding company benchmark, expanding market share.</t>
   </si>
   <si>
-    <t>SLIDE 11: MEDICAL REP / ADM QUARTERLY VELOCITY (AVERAGE MONTHLY Q3 2026 vs H1 2026 BASELINE)</t>
-  </si>
-  <si>
-    <t>National Velocity Benchmark: H1 Monthly Avg = 138,315 cans/mo | Q3 Monthly Avg = 156,126 cans/mo | Acceleration = +12.9% (+17,811 cans/mo)</t>
+    <t>SLIDE 11: 3-HORIZON RUN-RATE VELOCITY: Q3 2026 vs H1 2026 BASELINE vs 2025 FULL YEAR</t>
+  </si>
+  <si>
+    <t>National Velocity Benchmark: 2025 MoAvg = 103,385 | H1 MoAvg = 138,315 | Q3 MoAvg = 156,126 | Acceleration vs H1 = +12.9% | Expansion vs '25 = +51.0%</t>
   </si>
   <si>
     <t>Medical Rep / ADM Name</t>
   </si>
   <si>
+    <t>2025 MoAvg</t>
+  </si>
+  <si>
     <t>H1 MoAvg (Jan-Jun)</t>
   </si>
   <si>
     <t>Q3 MoAvg (Jul-Sep)</t>
   </si>
   <si>
-    <t>Net Diff / Mo</t>
-  </si>
-  <si>
-    <t>Velocity %</t>
+    <t>Net Diff vs H1</t>
+  </si>
+  <si>
+    <t>Q3 vs H1 Vel.%</t>
+  </si>
+  <si>
+    <t>Q3 vs '25 Grw.%</t>
+  </si>
+  <si>
+    <t>Q3 Share %</t>
   </si>
   <si>
     <t>Performance Tier</t>
@@ -649,7 +658,7 @@
     <t>National Medical Rep Team Benchmark</t>
   </si>
   <si>
-    <t>Overall company run-rate accelerated by +12.9% in Q3</t>
+    <t>Overall company run-rate accelerated by +12.9% in Q3 (+51.0% vs 2025 baseline)</t>
   </si>
   <si>
     <t>Tier 1: High Accelerator 🚀</t>
@@ -676,7 +685,7 @@
     <t>Quarterly run-rate deceleration; urgent trade stock replenishment and rep detailing call review.</t>
   </si>
   <si>
-    <t>PRODUCT PORTFOLIO VELOCITY BREAKDOWN (Q3 2026 vs H1 2026)</t>
+    <t>PRODUCT PORTFOLIO 3-HORIZON VELOCITY BREAKDOWN (2025 vs H1 2026 vs Q3 2026)</t>
   </si>
   <si>
     <t>SKU Code</t>
@@ -688,13 +697,16 @@
     <t>Category</t>
   </si>
   <si>
-    <t>H1 MoAvg (Units)</t>
-  </si>
-  <si>
-    <t>Q3 MoAvg (Units)</t>
-  </si>
-  <si>
-    <t>Diff / Mo</t>
+    <t>2025 MoAvg (Baseline)</t>
+  </si>
+  <si>
+    <t>H1 MoAvg (Baseline)</t>
+  </si>
+  <si>
+    <t>Q3 MoAvg (Run-Rate)</t>
+  </si>
+  <si>
+    <t>Diff vs H1</t>
   </si>
   <si>
     <t>Supply / Demand Dynamic</t>
@@ -706,7 +718,7 @@
     <t>Core Infant</t>
   </si>
   <si>
-    <t>Strong demand (+10.5%), supply stable</t>
+    <t>Strong demand (+14.9% vs H1 | +60.7% vs '25), supply stable</t>
   </si>
   <si>
     <t>P2</t>
@@ -715,7 +727,7 @@
     <t>Core Follow-up</t>
   </si>
   <si>
-    <t>Slight dip (-8.4%) from peak Q2 promotions</t>
+    <t>Compounding steady run-rate (+5.9% vs H1 | +75.1% vs '25)</t>
   </si>
   <si>
     <t>PG3</t>
@@ -724,7 +736,7 @@
     <t>Growing Up Milk</t>
   </si>
   <si>
-    <t>Supply constraint in Q3 (-80.6%)</t>
+    <t>Temporary supply constraint in Q3 (-80.6% vs H1 | -70.5% vs '25)</t>
   </si>
   <si>
     <t>LF</t>
@@ -733,7 +745,7 @@
     <t>Specialty Lactose Free</t>
   </si>
   <si>
-    <t>Supply quota restricted (-46.2%)</t>
+    <t>Quota restricted in Q3 (-46.2% vs H1 | -24.1% vs '25)</t>
   </si>
   <si>
     <t>HA</t>
@@ -742,7 +754,7 @@
     <t>Specialty Hypoallergenic</t>
   </si>
   <si>
-    <t>Surge in hospital demand (+102.4%)</t>
+    <t>Surge in hospital demand (+102.4% vs H1 | +119.6% vs '25)</t>
   </si>
   <si>
     <t>AR</t>
@@ -751,7 +763,7 @@
     <t>Specialty Anti-Regurgitation</t>
   </si>
   <si>
-    <t>Steady pediatric adoption (+30.1%)</t>
+    <t>Steady pediatric adoption (+27.7% vs H1 | -3.8% vs '25)</t>
   </si>
   <si>
     <t>AC</t>
@@ -760,7 +772,7 @@
     <t>Specialty Anti-Colic</t>
   </si>
   <si>
-    <t>Massive surge across clinics (+101.9%)</t>
+    <t>Massive surge across clinics (+101.9% vs H1 | +188.5% vs '25)</t>
   </si>
   <si>
     <t>MUM</t>
@@ -769,7 +781,7 @@
     <t>Maternal Nutrition</t>
   </si>
   <si>
-    <t>Niche pharmacy detailing (-10.4%)</t>
+    <t>Niche pharmacy detailing (-19.3% vs H1 | -30.0% vs '25)</t>
   </si>
   <si>
     <t>PS1</t>
@@ -778,7 +790,7 @@
     <t>Economy Infant</t>
   </si>
   <si>
-    <t>Heavy clinic uptake across Upper Egypt (+35.7%)</t>
+    <t>Heavy clinic uptake in Upper Egypt (+35.7% vs H1 | +32.9% vs '25)</t>
   </si>
   <si>
     <t>PS2</t>
@@ -787,7 +799,7 @@
     <t>Economy Follow-up</t>
   </si>
   <si>
-    <t>Stable rural demand (-6.3%)</t>
+    <t>Stable rural demand (-4.9% vs H1 | +33.0% vs '25)</t>
   </si>
   <si>
     <t>LBW</t>
@@ -796,7 +808,7 @@
     <t>Specialty Low Birth Weight</t>
   </si>
   <si>
-    <t>Severe temporary stockout in Q3 (-98.8%)</t>
+    <t>Severe temporary stockout in Q3 (-99.2% vs H1)</t>
   </si>
 </sst>
 </file>
@@ -967,7 +979,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1038,13 +1050,14 @@
     </xf>
     <xf numFmtId="168" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="169" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="169" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="169" fontId="17" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="169" fontId="18" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="169" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
@@ -3628,18 +3641,18 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="44" customWidth="1"/>
+    <col min="4" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>197</v>
       </c>
@@ -3651,8 +3664,11 @@
       <c r="G1" s="23"/>
       <c r="H1" s="23"/>
       <c r="I1" s="23"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="47" t="s">
         <v>198</v>
       </c>
@@ -3664,8 +3680,11 @@
       <c r="G2" s="47"/>
       <c r="H2" s="47"/>
       <c r="I2" s="47"/>
-    </row>
-    <row r="3" ht="25" customHeight="1" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+    </row>
+    <row r="3" ht="25" customHeight="1" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>150</v>
       </c>
@@ -3693,8 +3712,17 @@
       <c r="I3" s="9" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" s="37" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J3" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="37" t="s">
         <v>155</v>
       </c>
@@ -3702,28 +3730,37 @@
         <v>156</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D4" s="38">
+        <v>103385</v>
+      </c>
+      <c r="E4" s="38">
         <v>138315</v>
       </c>
-      <c r="E4" s="38">
+      <c r="F4" s="38">
         <v>156126</v>
       </c>
-      <c r="F4" s="48">
+      <c r="G4" s="48">
         <v>17811</v>
       </c>
-      <c r="G4" s="49">
+      <c r="H4" s="49">
         <v>0.12877128294111273</v>
       </c>
-      <c r="H4" s="37" t="s">
+      <c r="I4" s="49">
+        <v>0.5101417033418774</v>
+      </c>
+      <c r="J4" s="50">
+        <v>1</v>
+      </c>
+      <c r="K4" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="I4" s="37" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L4" s="37" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -3734,25 +3771,34 @@
         <v>75</v>
       </c>
       <c r="D5" s="12">
+        <v>7152</v>
+      </c>
+      <c r="E5" s="12">
         <v>8758</v>
       </c>
-      <c r="E5" s="12">
+      <c r="F5" s="12">
         <v>13898</v>
       </c>
-      <c r="F5" s="32">
+      <c r="G5" s="32">
         <v>5140</v>
       </c>
-      <c r="G5" s="50">
+      <c r="H5" s="51">
         <v>0.5868919844713405</v>
       </c>
-      <c r="H5" s="27" t="s">
-        <v>208</v>
-      </c>
-      <c r="I5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I5" s="52">
+        <v>0.9432326621923937</v>
+      </c>
+      <c r="J5" s="13">
+        <v>0.08901784456144396</v>
+      </c>
+      <c r="K5" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="L5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -3763,25 +3809,34 @@
         <v>87</v>
       </c>
       <c r="D6" s="12">
+        <v>9337</v>
+      </c>
+      <c r="E6" s="12">
         <v>10461</v>
       </c>
-      <c r="E6" s="12">
+      <c r="F6" s="12">
         <v>15472</v>
       </c>
-      <c r="F6" s="32">
+      <c r="G6" s="32">
         <v>5011</v>
       </c>
-      <c r="G6" s="50">
+      <c r="H6" s="51">
         <v>0.47901730236115103</v>
       </c>
-      <c r="H6" s="27" t="s">
-        <v>208</v>
-      </c>
-      <c r="I6" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I6" s="52">
+        <v>0.6570632965620649</v>
+      </c>
+      <c r="J6" s="13">
+        <v>0.0990994453198058</v>
+      </c>
+      <c r="K6" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="L6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
@@ -3792,25 +3847,34 @@
         <v>83</v>
       </c>
       <c r="D7" s="12">
+        <v>12877</v>
+      </c>
+      <c r="E7" s="12">
         <v>16459</v>
       </c>
-      <c r="E7" s="12">
+      <c r="F7" s="12">
         <v>23564</v>
       </c>
-      <c r="F7" s="32">
+      <c r="G7" s="32">
         <v>7105</v>
       </c>
-      <c r="G7" s="50">
+      <c r="H7" s="51">
         <v>0.43167871681147085</v>
       </c>
-      <c r="H7" s="27" t="s">
-        <v>208</v>
-      </c>
-      <c r="I7" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I7" s="52">
+        <v>0.8299293313660014</v>
+      </c>
+      <c r="J7" s="13">
+        <v>0.15092937755402688</v>
+      </c>
+      <c r="K7" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="L7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
@@ -3821,25 +3885,34 @@
         <v>73</v>
       </c>
       <c r="D8" s="12">
+        <v>12441</v>
+      </c>
+      <c r="E8" s="12">
         <v>14302</v>
       </c>
-      <c r="E8" s="12">
+      <c r="F8" s="12">
         <v>18041</v>
       </c>
-      <c r="F8" s="32">
+      <c r="G8" s="32">
         <v>3739</v>
       </c>
-      <c r="G8" s="51">
+      <c r="H8" s="53">
         <v>0.26143196755698495</v>
       </c>
-      <c r="H8" s="52" t="s">
-        <v>210</v>
-      </c>
-      <c r="I8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I8" s="52">
+        <v>0.4501245880556226</v>
+      </c>
+      <c r="J8" s="13">
+        <v>0.11555410373672546</v>
+      </c>
+      <c r="K8" s="54" t="s">
+        <v>213</v>
+      </c>
+      <c r="L8" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -3850,25 +3923,34 @@
         <v>85</v>
       </c>
       <c r="D9" s="12">
+        <v>14859</v>
+      </c>
+      <c r="E9" s="12">
         <v>22305</v>
       </c>
-      <c r="E9" s="12">
+      <c r="F9" s="12">
         <v>25694</v>
       </c>
-      <c r="F9" s="32">
+      <c r="G9" s="32">
         <v>3389</v>
       </c>
-      <c r="G9" s="51">
+      <c r="H9" s="53">
         <v>0.15193902712396334</v>
       </c>
-      <c r="H9" s="52" t="s">
-        <v>210</v>
-      </c>
-      <c r="I9" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I9" s="52">
+        <v>0.7291876976916347</v>
+      </c>
+      <c r="J9" s="13">
+        <v>0.16457220450149238</v>
+      </c>
+      <c r="K9" s="54" t="s">
+        <v>213</v>
+      </c>
+      <c r="L9" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
@@ -3879,25 +3961,34 @@
         <v>77</v>
       </c>
       <c r="D10" s="12">
+        <v>9951</v>
+      </c>
+      <c r="E10" s="12">
         <v>12895</v>
       </c>
-      <c r="E10" s="12">
+      <c r="F10" s="12">
         <v>13858</v>
       </c>
-      <c r="F10" s="32">
+      <c r="G10" s="32">
         <v>963</v>
       </c>
-      <c r="G10" s="53">
+      <c r="H10" s="55">
         <v>0.07468010856921281</v>
       </c>
-      <c r="H10" s="54" t="s">
-        <v>212</v>
-      </c>
-      <c r="I10" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I10" s="52">
+        <v>0.3926238568988041</v>
+      </c>
+      <c r="J10" s="13">
+        <v>0.08876164123848686</v>
+      </c>
+      <c r="K10" s="56" t="s">
+        <v>215</v>
+      </c>
+      <c r="L10" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7</v>
       </c>
@@ -3908,25 +3999,34 @@
         <v>71</v>
       </c>
       <c r="D11" s="12">
+        <v>7309</v>
+      </c>
+      <c r="E11" s="12">
         <v>10206</v>
       </c>
-      <c r="E11" s="12">
+      <c r="F11" s="12">
         <v>10314</v>
       </c>
-      <c r="F11" s="32">
+      <c r="G11" s="32">
         <v>108</v>
       </c>
-      <c r="G11" s="53">
+      <c r="H11" s="55">
         <v>0.010582010582010692</v>
       </c>
-      <c r="H11" s="54" t="s">
-        <v>212</v>
-      </c>
-      <c r="I11" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I11" s="52">
+        <v>0.41113695443973186</v>
+      </c>
+      <c r="J11" s="13">
+        <v>0.06606202682448792</v>
+      </c>
+      <c r="K11" s="56" t="s">
+        <v>215</v>
+      </c>
+      <c r="L11" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
@@ -3937,25 +4037,34 @@
         <v>79</v>
       </c>
       <c r="D12" s="12">
+        <v>15235</v>
+      </c>
+      <c r="E12" s="12">
         <v>20146</v>
       </c>
-      <c r="E12" s="12">
+      <c r="F12" s="12">
         <v>18614</v>
       </c>
-      <c r="F12" s="32">
+      <c r="G12" s="32">
         <v>-1532</v>
       </c>
-      <c r="G12" s="55">
+      <c r="H12" s="57">
         <v>-0.07604487243125191</v>
       </c>
-      <c r="H12" s="25" t="s">
-        <v>214</v>
-      </c>
-      <c r="I12" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I12" s="52">
+        <v>0.22179192648506718</v>
+      </c>
+      <c r="J12" s="13">
+        <v>0.1192242163380859</v>
+      </c>
+      <c r="K12" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="L12" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
@@ -3966,30 +4075,39 @@
         <v>81</v>
       </c>
       <c r="D13" s="12">
+        <v>14224</v>
+      </c>
+      <c r="E13" s="12">
         <v>22783</v>
       </c>
-      <c r="E13" s="12">
+      <c r="F13" s="12">
         <v>16671</v>
       </c>
-      <c r="F13" s="32">
+      <c r="G13" s="32">
         <v>-6112</v>
       </c>
-      <c r="G13" s="55">
+      <c r="H13" s="57">
         <v>-0.26827020146600533</v>
       </c>
-      <c r="H13" s="25" t="s">
-        <v>214</v>
-      </c>
-      <c r="I13" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I13" s="52">
+        <v>0.17203318335208095</v>
+      </c>
+      <c r="J13" s="13">
+        <v>0.10677913992544483</v>
+      </c>
+      <c r="K13" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="L13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -3998,360 +4116,471 @@
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
-    </row>
-    <row r="16" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+    </row>
+    <row r="16" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="I16" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="K16" s="9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L16" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B17" t="s">
         <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D17" s="12">
+        <v>27891</v>
+      </c>
+      <c r="E17" s="12">
         <v>39024</v>
       </c>
-      <c r="E17" s="12">
+      <c r="F17" s="12">
         <v>44832</v>
       </c>
-      <c r="F17" s="32">
+      <c r="G17" s="32">
         <v>5808</v>
       </c>
-      <c r="G17" s="56">
+      <c r="H17" s="52">
         <v>0.14883148831488313</v>
       </c>
-      <c r="H17" t="s">
-        <v>226</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="I17" s="52">
+        <v>0.6074002366354738</v>
+      </c>
+      <c r="J17" t="s">
+        <v>230</v>
+      </c>
+      <c r="K17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B18" t="s">
         <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D18" s="12">
+        <v>14775</v>
+      </c>
+      <c r="E18" s="12">
         <v>24418</v>
       </c>
-      <c r="E18" s="12">
+      <c r="F18" s="12">
         <v>25866</v>
       </c>
-      <c r="F18" s="32">
+      <c r="G18" s="32">
         <v>1448</v>
       </c>
-      <c r="G18" s="56">
+      <c r="H18" s="52">
         <v>0.05930051601277753</v>
       </c>
-      <c r="H18" t="s">
-        <v>229</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="I18" s="52">
+        <v>0.7506598984771573</v>
+      </c>
+      <c r="J18" t="s">
+        <v>233</v>
+      </c>
+      <c r="K18" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B19" t="s">
         <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D19" s="12">
+        <v>3515</v>
+      </c>
+      <c r="E19" s="12">
         <v>5338</v>
       </c>
-      <c r="E19" s="12">
+      <c r="F19" s="12">
         <v>1038</v>
       </c>
-      <c r="F19" s="32">
+      <c r="G19" s="32">
         <v>-4300</v>
       </c>
-      <c r="G19" s="57">
+      <c r="H19" s="58">
         <v>-0.8055451479955039</v>
       </c>
-      <c r="H19" t="s">
-        <v>232</v>
-      </c>
-      <c r="I19" t="s">
+      <c r="I19" s="52">
+        <v>-0.7046941678520626</v>
+      </c>
+      <c r="J19" t="s">
+        <v>236</v>
+      </c>
+      <c r="K19" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B20" t="s">
         <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D20" s="12">
+        <v>3073</v>
+      </c>
+      <c r="E20" s="12">
         <v>4335</v>
       </c>
-      <c r="E20" s="12">
+      <c r="F20" s="12">
         <v>2331</v>
       </c>
-      <c r="F20" s="32">
+      <c r="G20" s="32">
         <v>-2004</v>
       </c>
-      <c r="G20" s="57">
+      <c r="H20" s="58">
         <v>-0.46228373702422143</v>
       </c>
-      <c r="H20" t="s">
-        <v>235</v>
-      </c>
-      <c r="I20" t="s">
+      <c r="I20" s="52">
+        <v>-0.24145785876993164</v>
+      </c>
+      <c r="J20" t="s">
+        <v>239</v>
+      </c>
+      <c r="K20" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B21" t="s">
         <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D21" s="12">
+        <v>5436</v>
+      </c>
+      <c r="E21" s="12">
         <v>5899</v>
       </c>
-      <c r="E21" s="12">
+      <c r="F21" s="12">
         <v>11939</v>
       </c>
-      <c r="F21" s="32">
+      <c r="G21" s="32">
         <v>6040</v>
       </c>
-      <c r="G21" s="58">
+      <c r="H21" s="59">
         <v>1.0239023563315817</v>
       </c>
-      <c r="H21" t="s">
-        <v>238</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="I21" s="52">
+        <v>1.1962840323767474</v>
+      </c>
+      <c r="J21" t="s">
+        <v>242</v>
+      </c>
+      <c r="K21" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s">
         <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D22" s="12">
+        <v>6203</v>
+      </c>
+      <c r="E22" s="12">
         <v>4676</v>
       </c>
-      <c r="E22" s="12">
+      <c r="F22" s="12">
         <v>5970</v>
       </c>
-      <c r="F22" s="32">
+      <c r="G22" s="32">
         <v>1294</v>
       </c>
-      <c r="G22" s="58">
+      <c r="H22" s="59">
         <v>0.27673224978614197</v>
       </c>
-      <c r="H22" t="s">
-        <v>241</v>
-      </c>
-      <c r="I22" t="s">
+      <c r="I22" s="52">
+        <v>-0.03756246977269062</v>
+      </c>
+      <c r="J22" t="s">
+        <v>245</v>
+      </c>
+      <c r="K22" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B23" t="s">
         <v>60</v>
       </c>
       <c r="C23" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D23" s="12">
+        <v>5261</v>
+      </c>
+      <c r="E23" s="12">
         <v>7519</v>
       </c>
-      <c r="E23" s="12">
+      <c r="F23" s="12">
         <v>15180</v>
       </c>
-      <c r="F23" s="32">
+      <c r="G23" s="32">
         <v>7661</v>
       </c>
-      <c r="G23" s="58">
+      <c r="H23" s="59">
         <v>1.0188854900917677</v>
       </c>
-      <c r="H23" t="s">
-        <v>244</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="I23" s="52">
+        <v>1.8853830070328836</v>
+      </c>
+      <c r="J23" t="s">
+        <v>248</v>
+      </c>
+      <c r="K23" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s">
         <v>61</v>
       </c>
       <c r="C24" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D24" s="12">
+        <v>833</v>
+      </c>
+      <c r="E24" s="12">
         <v>722</v>
       </c>
-      <c r="E24" s="12">
+      <c r="F24" s="12">
         <v>583</v>
       </c>
-      <c r="F24" s="32">
+      <c r="G24" s="32">
         <v>-139</v>
       </c>
-      <c r="G24" s="57">
+      <c r="H24" s="58">
         <v>-0.19252077562326875</v>
       </c>
-      <c r="H24" t="s">
-        <v>247</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="I24" s="52">
+        <v>-0.30012004801920766</v>
+      </c>
+      <c r="J24" t="s">
+        <v>251</v>
+      </c>
+      <c r="K24" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s">
         <v>62</v>
       </c>
       <c r="C25" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D25" s="12">
+        <v>24791</v>
+      </c>
+      <c r="E25" s="12">
         <v>24280</v>
       </c>
-      <c r="E25" s="12">
+      <c r="F25" s="12">
         <v>32950</v>
       </c>
-      <c r="F25" s="32">
+      <c r="G25" s="32">
         <v>8670</v>
       </c>
-      <c r="G25" s="58">
+      <c r="H25" s="59">
         <v>0.35708401976935744</v>
       </c>
-      <c r="H25" t="s">
-        <v>250</v>
-      </c>
-      <c r="I25" t="s">
+      <c r="I25" s="52">
+        <v>0.329111371062079</v>
+      </c>
+      <c r="J25" t="s">
+        <v>254</v>
+      </c>
+      <c r="K25" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s">
         <v>63</v>
       </c>
       <c r="C26" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D26" s="12">
+        <v>11607</v>
+      </c>
+      <c r="E26" s="12">
         <v>16234</v>
       </c>
-      <c r="E26" s="12">
+      <c r="F26" s="12">
         <v>15438</v>
       </c>
-      <c r="F26" s="32">
+      <c r="G26" s="32">
         <v>-796</v>
       </c>
-      <c r="G26" s="57">
+      <c r="H26" s="58">
         <v>-0.04903289392632748</v>
       </c>
-      <c r="H26" t="s">
-        <v>253</v>
-      </c>
-      <c r="I26" t="s">
+      <c r="I26" s="52">
+        <v>0.33005944688550004</v>
+      </c>
+      <c r="J26" t="s">
+        <v>257</v>
+      </c>
+      <c r="K26" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s">
         <v>64</v>
       </c>
       <c r="C27" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D27" s="12">
+        <v>0</v>
+      </c>
+      <c r="E27" s="12">
         <v>5871</v>
       </c>
-      <c r="E27" s="12">
+      <c r="F27" s="12">
         <v>49</v>
       </c>
-      <c r="F27" s="32">
+      <c r="G27" s="32">
         <v>-5822</v>
       </c>
-      <c r="G27" s="57">
+      <c r="H27" s="58">
         <v>-0.9916538920115824</v>
       </c>
-      <c r="H27" t="s">
-        <v>256</v>
-      </c>
-      <c r="I27" t="s">
+      <c r="I27" s="52">
+        <v>1</v>
+      </c>
+      <c r="J27" t="s">
+        <v>260</v>
+      </c>
+      <c r="K27" t="s">
+        <v>15</v>
+      </c>
+      <c r="L27" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="B15:L15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
